--- a/AAII_Financials/Quarterly/EYEN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EYEN_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="92">
   <si>
     <t>EYEN</t>
   </si>
@@ -3456,19 +3456,19 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>100</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>4</v>
@@ -3732,10 +3732,10 @@
         <v>4700</v>
       </c>
       <c r="F45" s="3">
-        <v>4700</v>
+        <v>4800</v>
       </c>
       <c r="G45" s="3">
-        <v>2800</v>
+        <v>2900</v>
       </c>
       <c r="H45" s="3">
         <v>10600</v>
@@ -3910,25 +3910,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E47" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F47" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G47" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H47" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I47" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="J47" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>4</v>
@@ -4370,25 +4370,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>900</v>
+      </c>
+      <c r="E52" s="3">
+        <v>500</v>
+      </c>
+      <c r="F52" s="3">
         <v>700</v>
       </c>
-      <c r="E52" s="3">
-        <v>300</v>
-      </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
+        <v>800</v>
+      </c>
+      <c r="H52" s="3">
         <v>600</v>
       </c>
-      <c r="G52" s="3">
-        <v>700</v>
-      </c>
-      <c r="H52" s="3">
-        <v>400</v>
-      </c>
       <c r="I52" s="3">
+        <v>8600</v>
+      </c>
+      <c r="J52" s="3">
         <v>8400</v>
-      </c>
-      <c r="J52" s="3">
-        <v>8300</v>
       </c>
       <c r="K52" s="3">
         <v>500</v>

--- a/AAII_Financials/Quarterly/EYEN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EYEN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="92">
   <si>
     <t>EYEN</t>
   </si>
@@ -656,157 +656,164 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I8" s="3">
         <v>0</v>
@@ -815,25 +822,25 @@
         <v>0</v>
       </c>
       <c r="K8" s="3">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3">
         <v>10000</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
-      </c>
-      <c r="M8" s="3">
-        <v>2000</v>
-      </c>
       <c r="N8" s="3">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="O8" s="3">
         <v>2000</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>4</v>
+      <c r="P8" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>2000</v>
       </c>
       <c r="R8" s="3" t="s">
         <v>4</v>
@@ -844,11 +851,11 @@
       <c r="T8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U8" s="3">
-        <v>0</v>
-      </c>
-      <c r="V8" s="3">
-        <v>0</v>
+      <c r="U8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W8" s="3">
         <v>0</v>
@@ -880,19 +887,25 @@
       <c r="AF8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
         <v>0</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>4</v>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>4</v>
@@ -912,20 +925,20 @@
       <c r="L9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M9" s="3">
-        <v>800</v>
-      </c>
-      <c r="N9" s="3">
-        <v>800</v>
+      <c r="M9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O9" s="3">
         <v>800</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>4</v>
+      <c r="P9" s="3">
+        <v>800</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>800</v>
       </c>
       <c r="R9" s="3" t="s">
         <v>4</v>
@@ -972,19 +985,25 @@
       <c r="AF9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>4</v>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>4</v>
@@ -1004,20 +1023,20 @@
       <c r="L10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M10" s="3">
-        <v>1200</v>
-      </c>
-      <c r="N10" s="3">
-        <v>1200</v>
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O10" s="3">
         <v>1200</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>4</v>
+      <c r="P10" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>1200</v>
       </c>
       <c r="R10" s="3" t="s">
         <v>4</v>
@@ -1064,8 +1083,14 @@
       <c r="AF10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,100 +1123,108 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E12" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F12" s="3">
         <v>3600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>2800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>2500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>2300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>3900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>3600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>3700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>3200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>3600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>3700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>4300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>3400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>3400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>2900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>3600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>3300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>3200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>3600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>4000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>4100</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>2500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>2400</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>2100</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>1700</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>600</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>800</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>900</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>1000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,44 +1315,50 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
+      <c r="E14" s="3">
+        <v>0</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-500</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1332,11 +1371,11 @@
       <c r="R14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1374,8 +1413,14 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1466,8 +1511,14 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,145 +1548,153 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E17" s="3">
+        <v>7500</v>
+      </c>
+      <c r="F17" s="3">
         <v>6500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>6000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>5500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>5400</v>
-      </c>
-      <c r="H17" s="3">
-        <v>7200</v>
-      </c>
-      <c r="I17" s="3">
-        <v>7100</v>
       </c>
       <c r="J17" s="3">
         <v>7200</v>
       </c>
       <c r="K17" s="3">
+        <v>7100</v>
+      </c>
+      <c r="L17" s="3">
+        <v>7200</v>
+      </c>
+      <c r="M17" s="3">
         <v>6900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>5500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>6800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>7400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>6200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>5100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>5000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>5500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>5300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>4700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>5400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>6000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>6200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>4300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>3300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>3400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>2200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>1000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>1100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>1200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G18" s="3">
+      <c r="E18" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I18" s="3">
         <v>-5400</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-7200</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-7100</v>
       </c>
       <c r="J18" s="3">
         <v>-7200</v>
       </c>
       <c r="K18" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="L18" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="M18" s="3">
         <v>3100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-5500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-4800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-5400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-4200</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>4</v>
       </c>
@@ -1645,44 +1704,50 @@
       <c r="T18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W18" s="3">
         <v>-5400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-6000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-6200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,52 +1780,54 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="E20" s="3">
         <v>200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="F20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20" s="3">
+        <v>200</v>
+      </c>
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>4</v>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
       </c>
       <c r="R20" s="3" t="s">
         <v>4</v>
@@ -1771,11 +1838,11 @@
       <c r="T20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
-      <c r="V20" s="3">
-        <v>0</v>
+      <c r="U20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W20" s="3">
         <v>0</v>
@@ -1807,53 +1874,59 @@
       <c r="AF20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G21" s="3">
+      <c r="E21" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I21" s="3">
         <v>-5100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-7000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-7000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-7100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>3200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-5400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-4700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-5300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-4200</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1863,44 +1936,50 @@
       <c r="T21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W21" s="3">
         <v>-5300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-5900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-6200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-2100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1908,22 +1987,22 @@
         <v>700</v>
       </c>
       <c r="E22" s="3">
+        <v>700</v>
+      </c>
+      <c r="F22" s="3">
+        <v>700</v>
+      </c>
+      <c r="G22" s="3">
         <v>600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>200</v>
-      </c>
-      <c r="I22" s="3">
-        <v>200</v>
-      </c>
-      <c r="J22" s="3">
-        <v>100</v>
       </c>
       <c r="K22" s="3">
         <v>200</v>
@@ -1932,13 +2011,13 @@
         <v>100</v>
       </c>
       <c r="M22" s="3">
+        <v>200</v>
+      </c>
+      <c r="N22" s="3">
         <v>100</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
       <c r="O22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1949,11 +2028,11 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T22" s="3" t="s">
-        <v>4</v>
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
+        <v>0</v>
       </c>
       <c r="U22" s="3" t="s">
         <v>4</v>
@@ -1967,11 +2046,11 @@
       <c r="X22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>0</v>
+      <c r="Y22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA22" s="3">
         <v>0</v>
@@ -1991,100 +2070,112 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="F23" s="3">
         <v>-7300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-6200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-5700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-6100</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-7300</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-7200</v>
       </c>
       <c r="J23" s="3">
         <v>-7300</v>
       </c>
       <c r="K23" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="L23" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="M23" s="3">
         <v>3000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-5600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-4800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-5400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-4200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-5000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-5500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-5200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-4600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-5300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-5900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-6200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2175,8 +2266,14 @@
       <c r="AF24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2364,210 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="F26" s="3">
         <v>-7300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-6200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-5700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-6100</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-7300</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-7200</v>
       </c>
       <c r="J26" s="3">
         <v>-7300</v>
       </c>
       <c r="K26" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="L26" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="M26" s="3">
         <v>3000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-5600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-4800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-5400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-4200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-5000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-5500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-5200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-4600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-5300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-5900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-6200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="F27" s="3">
         <v>-7300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-6200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-5700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-6100</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-7300</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-7200</v>
       </c>
       <c r="J27" s="3">
         <v>-7300</v>
       </c>
       <c r="K27" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="L27" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="M27" s="3">
         <v>3000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-5600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-4800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-5400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-4200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-5000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-5500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-5200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-4600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-5300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-5900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-6200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2658,14 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2756,14 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2854,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,52 +2952,58 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="E32" s="3">
         <v>-200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="F32" s="3">
+        <v>100</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q32" s="3" t="s">
-        <v>4</v>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
       </c>
       <c r="R32" s="3" t="s">
         <v>4</v>
@@ -2875,11 +3014,11 @@
       <c r="T32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
-      <c r="V32" s="3">
-        <v>0</v>
+      <c r="U32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W32" s="3">
         <v>0</v>
@@ -2911,100 +3050,112 @@
       <c r="AF32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="F33" s="3">
         <v>-7300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-6200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-5700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-6100</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-7300</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-7200</v>
       </c>
       <c r="J33" s="3">
         <v>-7300</v>
       </c>
       <c r="K33" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="L33" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="M33" s="3">
         <v>3000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-5600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-4800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-5400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-4200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-5000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-5500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-5200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-4600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-5300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-5900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-6200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3246,215 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="F35" s="3">
         <v>-7300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-6200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-5700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-6100</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-7300</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-7200</v>
       </c>
       <c r="J35" s="3">
         <v>-7300</v>
       </c>
       <c r="K35" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="L35" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="M35" s="3">
         <v>3000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-5600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-4800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-5400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-4200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-5000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-5500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-5200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-4600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-5300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-5900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-6200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3487,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,100 +3523,108 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>14800</v>
+      </c>
+      <c r="F41" s="3">
         <v>20700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>17500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>18500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>22900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>17400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>21500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>26700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>19500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>13500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>27200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>24900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>28400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>22900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>10200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>13700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>14200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>18300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>9200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>14300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>19700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>21000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>24600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>27600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>5200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>7400</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE41" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3470,17 +3649,17 @@
       <c r="J42" s="3">
         <v>0</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
-      <c r="N42" s="3">
-        <v>0</v>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O42" s="3">
         <v>0</v>
@@ -3536,58 +3715,64 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>600</v>
+      </c>
+      <c r="E43" s="3">
+        <v>600</v>
+      </c>
+      <c r="F43" s="3">
         <v>900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>1600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>1800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>2100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>1200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>3100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>200</v>
-      </c>
-      <c r="R43" s="3">
-        <v>100</v>
-      </c>
-      <c r="S43" s="3">
-        <v>100</v>
       </c>
       <c r="T43" s="3">
         <v>100</v>
@@ -3598,11 +3783,11 @@
       <c r="V43" s="3">
         <v>100</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X43" s="3" t="s">
-        <v>4</v>
+      <c r="W43" s="3">
+        <v>100</v>
+      </c>
+      <c r="X43" s="3">
+        <v>100</v>
       </c>
       <c r="Y43" s="3" t="s">
         <v>4</v>
@@ -3610,11 +3795,11 @@
       <c r="Z43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA43" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB43" s="3">
-        <v>0</v>
+      <c r="AA43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC43" s="3">
         <v>0</v>
@@ -3628,19 +3813,25 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E44" s="3">
         <v>100</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>4</v>
+      <c r="F44" s="3">
+        <v>100</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>4</v>
@@ -3654,11 +3845,11 @@
       <c r="J44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3720,192 +3911,210 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E45" s="3">
+        <v>5100</v>
+      </c>
+      <c r="F45" s="3">
         <v>4900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>4700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>4800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>2900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>10600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>2800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>1800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>8300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>8700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>1900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>1900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>2300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>400</v>
       </c>
-      <c r="AA45" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD45" s="3">
         <v>100</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE45" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>20700</v>
+      </c>
+      <c r="F46" s="3">
         <v>26500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>23300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>24900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>27600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>29400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>25600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>30400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>29900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>23500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>29500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>28000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>33400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>25400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>11000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>14500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>14300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>18700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>9800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>14900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>19900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>21300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>24800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>28000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>5300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>7500</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE46" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3930,17 +4139,17 @@
       <c r="J47" s="3">
         <v>0</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="K47" s="3">
+        <v>0</v>
+      </c>
+      <c r="L47" s="3">
+        <v>0</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
@@ -3996,68 +4205,74 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E48" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F48" s="3">
         <v>5300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>5600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>3700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>2600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>1300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1400</v>
-      </c>
-      <c r="J48" s="3">
-        <v>1400</v>
-      </c>
-      <c r="K48" s="3">
-        <v>1300</v>
       </c>
       <c r="L48" s="3">
         <v>1400</v>
       </c>
       <c r="M48" s="3">
+        <v>1300</v>
+      </c>
+      <c r="N48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="O48" s="3">
         <v>1000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>100</v>
       </c>
-      <c r="U48" s="3">
-        <v>0</v>
-      </c>
-      <c r="V48" s="3">
-        <v>0</v>
-      </c>
       <c r="W48" s="3">
         <v>0</v>
       </c>
@@ -4076,11 +4291,11 @@
       <c r="AB48" s="3">
         <v>0</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD48" s="3" t="s">
-        <v>4</v>
+      <c r="AC48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD48" s="3">
+        <v>0</v>
       </c>
       <c r="AE48" s="3" t="s">
         <v>4</v>
@@ -4088,19 +4303,25 @@
       <c r="AF48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E49" s="3">
         <v>2100</v>
       </c>
-      <c r="E49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>4</v>
+      <c r="F49" s="3">
+        <v>2100</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>4</v>
@@ -4114,11 +4335,11 @@
       <c r="J49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
-      </c>
-      <c r="L49" s="3">
-        <v>0</v>
+      <c r="K49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M49" s="3">
         <v>0</v>
@@ -4180,8 +4401,14 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4499,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,8 +4597,14 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4373,31 +4612,31 @@
         <v>900</v>
       </c>
       <c r="E52" s="3">
+        <v>900</v>
+      </c>
+      <c r="F52" s="3">
+        <v>900</v>
+      </c>
+      <c r="G52" s="3">
         <v>500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>8600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>8400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>500</v>
-      </c>
-      <c r="L52" s="3">
-        <v>100</v>
-      </c>
-      <c r="M52" s="3">
-        <v>100</v>
       </c>
       <c r="N52" s="3">
         <v>100</v>
@@ -4421,43 +4660,49 @@
         <v>100</v>
       </c>
       <c r="U52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="V52" s="3">
         <v>100</v>
       </c>
       <c r="W52" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="X52" s="3">
         <v>100</v>
       </c>
       <c r="Y52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="3">
         <v>300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>100</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE52" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4793,112 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>26200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>28800</v>
+      </c>
+      <c r="F54" s="3">
         <v>34900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>29300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>29300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>31000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>31400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>35600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>40200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>31700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>25000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>30600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>28900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>33900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>25800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>11400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>14900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>14700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>18900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>10000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>15000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>20000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>21500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>24800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>28000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>5600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>7700</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE54" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4931,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,154 +4967,162 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1400</v>
+        <v>2100</v>
       </c>
       <c r="E57" s="3">
-        <v>1300</v>
+        <v>1800</v>
       </c>
       <c r="F57" s="3">
         <v>1400</v>
       </c>
       <c r="G57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H57" s="3">
         <v>1400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J57" s="3">
         <v>1100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>2700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>1600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>1700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>1700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>1800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>1500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>1500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>1100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>1300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>1500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>1600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>1800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>2100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>1500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>300</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE57" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E58" s="3">
+        <v>5300</v>
+      </c>
+      <c r="F58" s="3">
         <v>3000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>7200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>7400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>7700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>7200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>7300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>400</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>4</v>
       </c>
@@ -4868,11 +5135,11 @@
       <c r="X58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z58" s="3">
-        <v>0</v>
+      <c r="Y58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA58" s="3">
         <v>0</v>
@@ -4892,213 +5159,231 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F59" s="3">
         <v>2100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>2700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>2700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>2400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>11800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>11900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>13800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>16600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>5100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>1400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>1600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>300</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE59" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>16500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>9500</v>
+      </c>
+      <c r="F60" s="3">
         <v>6500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>4100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>4900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>4500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>11000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>12000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>10400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>11200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>20700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>14600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>16400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>18200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>6700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>2800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>2500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>2900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>2400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>2400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>2500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>3100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>1700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>1300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>1100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>600</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE60" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E61" s="3">
+        <v>9000</v>
+      </c>
+      <c r="F61" s="3">
         <v>11100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>13200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>7500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>8400</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -5109,26 +5394,26 @@
         <v>0</v>
       </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>7000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>300</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -5168,32 +5453,38 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E62" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F62" s="3">
         <v>1400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>1600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>1100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>100</v>
       </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
-      </c>
       <c r="K62" s="3">
         <v>0</v>
       </c>
@@ -5236,32 +5527,38 @@
       <c r="X62" s="3">
         <v>0</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB62" s="3">
+      <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD62" s="3">
         <v>6400</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE62" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5649,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5747,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5845,112 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>24400</v>
+      </c>
+      <c r="E66" s="3">
+        <v>19800</v>
+      </c>
+      <c r="F66" s="3">
         <v>19100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>18800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>13500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>13800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>11100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>12000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>10400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>11200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>20700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>21600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>16700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>18600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>7200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>3100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>2600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>3000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>2500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>2400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>2600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>3100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>1700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>1300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>1100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>7000</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE66" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5983,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +6077,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6175,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6273,14 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6371,112 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-156400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-145500</v>
+      </c>
+      <c r="F72" s="3">
         <v>-137500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-130200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-124000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-118200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-112100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-104800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-97600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-90200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-93200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-87600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-82800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-77400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-73200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-68100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-63100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-57700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-52400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-47800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-42400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-36500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-30300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-26000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-22700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-19300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-17100</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE72" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6567,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6665,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6763,112 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>15800</v>
+        <v>1800</v>
       </c>
       <c r="E76" s="3">
-        <v>10500</v>
+        <v>9000</v>
       </c>
       <c r="F76" s="3">
         <v>15800</v>
       </c>
       <c r="G76" s="3">
+        <v>10500</v>
+      </c>
+      <c r="H76" s="3">
+        <v>15800</v>
+      </c>
+      <c r="I76" s="3">
         <v>17200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>20300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>23600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>29800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>20500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>4200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>9000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>12100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>15300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>18700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>8300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>12300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>11700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>16400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>7600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>12500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>16900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>19700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>23500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>26900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>5100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>700</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE76" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6959,215 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="F81" s="3">
         <v>-7300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-6200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-5700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-6100</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-7300</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-7200</v>
       </c>
       <c r="J81" s="3">
         <v>-7300</v>
       </c>
       <c r="K81" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="L81" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="M81" s="3">
         <v>3000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-5600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-4800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-5400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-4200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-5000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-5500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-5200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-4600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-5300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-5900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-6200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,19 +7200,21 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>200</v>
+      </c>
+      <c r="E83" s="3">
         <v>300</v>
       </c>
-      <c r="E83" s="3">
-        <v>100</v>
-      </c>
       <c r="F83" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="G83" s="3">
         <v>100</v>
@@ -6838,10 +7235,10 @@
         <v>100</v>
       </c>
       <c r="M83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O83" s="3">
         <v>0</v>
@@ -6897,8 +7294,14 @@
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7392,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7490,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7588,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7686,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7784,112 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="F89" s="3">
         <v>-5800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-4700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-7000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-5400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-6800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-4700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-8200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-5900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-5100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-5300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-4600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>5500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-1900</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="R89" s="3">
-        <v>-5900</v>
       </c>
       <c r="S89" s="3">
         <v>-4000</v>
       </c>
       <c r="T89" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="U89" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="V89" s="3">
         <v>-3900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-5100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-5900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-4100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>-900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,64 +7922,66 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-1200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-300</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-200</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-200</v>
       </c>
       <c r="J91" s="3">
         <v>-200</v>
       </c>
       <c r="K91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-100</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>0</v>
       </c>
       <c r="R91" s="3">
         <v>-100</v>
       </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U91" s="3" t="s">
-        <v>4</v>
+      <c r="U91" s="3">
+        <v>-100</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>4</v>
@@ -7557,11 +7998,11 @@
       <c r="Z91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB91" s="3">
-        <v>0</v>
+      <c r="AA91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC91" s="3">
         <v>0</v>
@@ -7575,8 +8016,14 @@
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +8114,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,73 +8212,79 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-1300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-300</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-200</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-200</v>
       </c>
       <c r="J94" s="3">
         <v>-200</v>
       </c>
       <c r="K94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M94" s="3">
         <v>-500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-100</v>
-      </c>
-      <c r="P94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>0</v>
       </c>
       <c r="R94" s="3">
         <v>-100</v>
       </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>-100</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U94" s="3" t="s">
-        <v>4</v>
+      <c r="U94" s="3">
+        <v>-100</v>
       </c>
       <c r="V94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
-      <c r="X94" s="3">
-        <v>0</v>
+      <c r="W94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y94" s="3">
         <v>0</v>
@@ -7851,8 +8310,14 @@
       <c r="AF94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8350,10 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7977,8 +8444,14 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8542,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8640,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,100 +8738,112 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>600</v>
+      </c>
+      <c r="F100" s="3">
         <v>10800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>5000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>3400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>3300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>2900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>15600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>12300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>7900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>1500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>14700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>5500</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>13000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>2800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>100</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>24700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>6800</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
       <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
         <v>100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8437,96 +8934,108 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="F102" s="3">
         <v>3200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-1000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-4400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-2400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-4100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-5200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>7300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>6000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-5800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>2300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-3500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>5500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>12700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-3500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-4100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>9100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-5100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-5400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-1300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-3500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>22400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>5900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>1800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EYEN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EYEN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="92">
   <si>
     <t>EYEN</t>
   </si>
@@ -656,147 +656,151 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -809,14 +813,14 @@
       <c r="F8" s="3">
         <v>0</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>4</v>
+      <c r="G8" s="3">
+        <v>0</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I8" s="3">
-        <v>0</v>
+      <c r="I8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J8" s="3">
         <v>0</v>
@@ -828,13 +832,13 @@
         <v>0</v>
       </c>
       <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3">
         <v>10000</v>
       </c>
-      <c r="N8" s="3">
-        <v>0</v>
-      </c>
       <c r="O8" s="3">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="P8" s="3">
         <v>2000</v>
@@ -842,8 +846,8 @@
       <c r="Q8" s="3">
         <v>2000</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>4</v>
+      <c r="R8" s="3">
+        <v>2000</v>
       </c>
       <c r="S8" s="3" t="s">
         <v>4</v>
@@ -857,8 +861,8 @@
       <c r="V8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W8" s="3">
-        <v>0</v>
+      <c r="W8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X8" s="3">
         <v>0</v>
@@ -893,13 +897,16 @@
       <c r="AH8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E9" s="3">
         <v>0</v>
@@ -907,8 +914,8 @@
       <c r="F9" s="3">
         <v>0</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>4</v>
+      <c r="G9" s="3">
+        <v>0</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>4</v>
@@ -931,8 +938,8 @@
       <c r="N9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O9" s="3">
-        <v>800</v>
+      <c r="O9" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P9" s="3">
         <v>800</v>
@@ -940,8 +947,8 @@
       <c r="Q9" s="3">
         <v>800</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>4</v>
+      <c r="R9" s="3">
+        <v>800</v>
       </c>
       <c r="S9" s="3" t="s">
         <v>4</v>
@@ -991,8 +998,11 @@
       <c r="AH9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1005,8 +1015,8 @@
       <c r="F10" s="3">
         <v>0</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>4</v>
+      <c r="G10" s="3">
+        <v>0</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>4</v>
@@ -1029,8 +1039,8 @@
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O10" s="3">
-        <v>1200</v>
+      <c r="O10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P10" s="3">
         <v>1200</v>
@@ -1038,8 +1048,8 @@
       <c r="Q10" s="3">
         <v>1200</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>4</v>
+      <c r="R10" s="3">
+        <v>1200</v>
       </c>
       <c r="S10" s="3" t="s">
         <v>4</v>
@@ -1089,8 +1099,11 @@
       <c r="AH10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1125,106 +1138,110 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E12" s="3">
         <v>4400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>4100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>3600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>2500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>2300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>3900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>4300</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>3400</v>
       </c>
       <c r="R12" s="3">
         <v>3400</v>
       </c>
       <c r="S12" s="3">
+        <v>3400</v>
+      </c>
+      <c r="T12" s="3">
         <v>2900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>3600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>3300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>3200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>3600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>4000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>4100</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>2500</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>2400</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>2100</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>1700</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>600</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>800</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>900</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>1000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,19 +1338,22 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>4</v>
@@ -1341,27 +1361,27 @@
       <c r="H14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>4</v>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>-500</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1377,8 +1397,8 @@
       <c r="T14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1419,8 +1439,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,106 +1576,110 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E17" s="3">
         <v>10300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>7400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>6200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>6000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>6200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1657,47 +1687,47 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-7500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-6500</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I18" s="3">
+      <c r="I18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J18" s="3">
         <v>-5400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-7200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-7100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-7200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-5500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-4800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-4200</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>4</v>
       </c>
@@ -1710,44 +1740,47 @@
       <c r="V18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W18" s="3">
+      <c r="W18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X18" s="3">
         <v>-5400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-6000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-6200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-3300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-1100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-1200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,8 +1815,9 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1791,35 +1825,35 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I20" s="3">
+      <c r="I20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
@@ -1829,8 +1863,8 @@
       <c r="Q20" s="3">
         <v>0</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>4</v>
+      <c r="R20" s="3">
+        <v>0</v>
       </c>
       <c r="S20" s="3" t="s">
         <v>4</v>
@@ -1844,8 +1878,8 @@
       <c r="V20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
+      <c r="W20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X20" s="3">
         <v>0</v>
@@ -1880,8 +1914,11 @@
       <c r="AH20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1889,47 +1926,47 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="F21" s="3">
         <v>-7000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-6300</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I21" s="3">
+      <c r="I21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J21" s="3">
         <v>-5100</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-7000</v>
       </c>
       <c r="K21" s="3">
         <v>-7000</v>
       </c>
       <c r="L21" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="M21" s="3">
         <v>-7100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-5400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-4700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-4200</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1942,44 +1979,47 @@
       <c r="V21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X21" s="3">
         <v>-5300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-5900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-6200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-3300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-1100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-1200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1993,34 +2033,34 @@
         <v>700</v>
       </c>
       <c r="G22" s="3">
+        <v>700</v>
+      </c>
+      <c r="H22" s="3">
         <v>600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>900</v>
-      </c>
-      <c r="J22" s="3">
-        <v>200</v>
       </c>
       <c r="K22" s="3">
         <v>200</v>
       </c>
       <c r="L22" s="3">
+        <v>200</v>
+      </c>
+      <c r="M22" s="3">
         <v>100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>200</v>
-      </c>
-      <c r="N22" s="3">
-        <v>100</v>
       </c>
       <c r="O22" s="3">
         <v>100</v>
       </c>
       <c r="P22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -2034,8 +2074,8 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>4</v>
+      <c r="U22" s="3">
+        <v>0</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>4</v>
@@ -2052,8 +2092,8 @@
       <c r="Z22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA22" s="3">
-        <v>0</v>
+      <c r="AA22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB22" s="3">
         <v>0</v>
@@ -2076,106 +2116,112 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-10900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-8000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-7300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-6200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-5700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-6100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-7300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-7200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-7300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-5600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-4800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-4200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-5100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-5000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-5500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-5200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-4600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-5300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-5900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-6200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-3300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-1100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-1200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2272,8 +2318,11 @@
       <c r="AH24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-10900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-8000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-7300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-6200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-5700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-6100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-7300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-7200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-7300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-5600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-4800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-4200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-5100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-5000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-5500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-5200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-4600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-5300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-5900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-6200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-3300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-1100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-1200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-10900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-8000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-7300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-6200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-5700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-6100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-7300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-7200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-7300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-5600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-4800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-4200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-5100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-5000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-5500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-5200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-4600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-5300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-5900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-6200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-3300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-1100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-1200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,8 +3025,11 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2967,35 +3037,35 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I32" s="3">
+      <c r="I32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
@@ -3005,8 +3075,8 @@
       <c r="Q32" s="3">
         <v>0</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>4</v>
+      <c r="R32" s="3">
+        <v>0</v>
       </c>
       <c r="S32" s="3" t="s">
         <v>4</v>
@@ -3020,8 +3090,8 @@
       <c r="V32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
+      <c r="W32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X32" s="3">
         <v>0</v>
@@ -3056,106 +3126,112 @@
       <c r="AH32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-10900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-8000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-7300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-6200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-5700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-6100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-7300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-7200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-7300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-5600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-4800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-4200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-5100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-5000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-5500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-5200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-4600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-5300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-5900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-6200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-3300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-1100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-1200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-10900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-8000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-7300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-6200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-5700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-6100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-7300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-7200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-7300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-5600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-4800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-4200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-5100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-5000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-5500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-5200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-4600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-5300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-5900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-6200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-3300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-1100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-1200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,95 +3611,96 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E41" s="3">
         <v>8000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>14800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>20700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>17500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>18500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>22900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>17400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>21500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>26700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>19500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>13500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>27200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>24900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>28400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>22900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>10200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>13700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>14200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>18300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>9200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>14300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>19700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>21000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>24600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>27600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>7400</v>
       </c>
-      <c r="AE41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF41" s="3" t="s">
         <v>4</v>
       </c>
@@ -3623,8 +3710,11 @@
       <c r="AH41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3655,14 +3745,14 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>4</v>
+      <c r="M42" s="3">
+        <v>0</v>
       </c>
       <c r="N42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
+      <c r="O42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P42" s="3">
         <v>0</v>
@@ -3721,61 +3811,64 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="E43" s="3">
         <v>600</v>
       </c>
       <c r="F43" s="3">
+        <v>600</v>
+      </c>
+      <c r="G43" s="3">
         <v>900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1300</v>
-      </c>
-      <c r="O43" s="3">
-        <v>1200</v>
       </c>
       <c r="P43" s="3">
         <v>1200</v>
       </c>
       <c r="Q43" s="3">
+        <v>1200</v>
+      </c>
+      <c r="R43" s="3">
         <v>3100</v>
-      </c>
-      <c r="R43" s="3">
-        <v>200</v>
       </c>
       <c r="S43" s="3">
         <v>200</v>
       </c>
       <c r="T43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="U43" s="3">
         <v>100</v>
@@ -3789,8 +3882,8 @@
       <c r="X43" s="3">
         <v>100</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>4</v>
+      <c r="Y43" s="3">
+        <v>100</v>
       </c>
       <c r="Z43" s="3" t="s">
         <v>4</v>
@@ -3801,8 +3894,8 @@
       <c r="AB43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC43" s="3">
-        <v>0</v>
+      <c r="AC43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD43" s="3">
         <v>0</v>
@@ -3819,22 +3912,25 @@
       <c r="AH43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E44" s="3">
         <v>3500</v>
-      </c>
-      <c r="E44" s="3">
-        <v>100</v>
       </c>
       <c r="F44" s="3">
         <v>100</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>4</v>
+      <c r="G44" s="3">
+        <v>100</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>4</v>
@@ -3851,8 +3947,8 @@
       <c r="L44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3917,95 +4013,98 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E45" s="3">
         <v>2400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>10600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>8300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>8700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1100</v>
-      </c>
-      <c r="P45" s="3">
-        <v>1900</v>
       </c>
       <c r="Q45" s="3">
         <v>1900</v>
       </c>
       <c r="R45" s="3">
+        <v>1900</v>
+      </c>
+      <c r="S45" s="3">
         <v>2300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>300</v>
-      </c>
-      <c r="W45" s="3">
-        <v>500</v>
       </c>
       <c r="X45" s="3">
         <v>500</v>
       </c>
       <c r="Y45" s="3">
+        <v>500</v>
+      </c>
+      <c r="Z45" s="3">
         <v>100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>400</v>
       </c>
-      <c r="AC45" s="3">
-        <v>0</v>
-      </c>
       <c r="AD45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE45" s="3">
         <v>100</v>
       </c>
-      <c r="AE45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF45" s="3" t="s">
         <v>4</v>
       </c>
@@ -4015,95 +4114,98 @@
       <c r="AH45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E46" s="3">
         <v>14500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>20700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>26500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>23300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>24900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>27600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>29400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>25600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>30400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>29900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>23500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>29500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>28000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>33400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>25400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>11000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>14500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>14300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>18700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>9800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>14900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>19900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>21300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>24800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>28000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>5300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>7500</v>
       </c>
-      <c r="AE46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF46" s="3" t="s">
         <v>4</v>
       </c>
@@ -4113,8 +4215,11 @@
       <c r="AH46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4145,14 +4250,14 @@
       <c r="L47" s="3">
         <v>0</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>4</v>
+      <c r="M47" s="3">
+        <v>0</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -4211,71 +4316,74 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E48" s="3">
         <v>4700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1300</v>
-      </c>
-      <c r="K48" s="3">
-        <v>1400</v>
       </c>
       <c r="L48" s="3">
         <v>1400</v>
       </c>
       <c r="M48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="N48" s="3">
         <v>1300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>700</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>400</v>
       </c>
       <c r="R48" s="3">
         <v>400</v>
       </c>
       <c r="S48" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="T48" s="3">
         <v>300</v>
       </c>
       <c r="U48" s="3">
+        <v>300</v>
+      </c>
+      <c r="V48" s="3">
         <v>200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>100</v>
       </c>
-      <c r="W48" s="3">
-        <v>0</v>
-      </c>
       <c r="X48" s="3">
         <v>0</v>
       </c>
@@ -4297,8 +4405,8 @@
       <c r="AD48" s="3">
         <v>0</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>4</v>
+      <c r="AE48" s="3">
+        <v>0</v>
       </c>
       <c r="AF48" s="3" t="s">
         <v>4</v>
@@ -4309,8 +4417,11 @@
       <c r="AH48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4318,13 +4429,13 @@
         <v>6100</v>
       </c>
       <c r="E49" s="3">
-        <v>2100</v>
+        <v>6100</v>
       </c>
       <c r="F49" s="3">
         <v>2100</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>4</v>
+      <c r="G49" s="3">
+        <v>2100</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>4</v>
@@ -4341,8 +4452,8 @@
       <c r="L49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
+      <c r="M49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N49" s="3">
         <v>0</v>
@@ -4407,8 +4518,11 @@
       <c r="AH49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,13 +4720,16 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="E52" s="3">
         <v>900</v>
@@ -4618,28 +4738,28 @@
         <v>900</v>
       </c>
       <c r="G52" s="3">
+        <v>900</v>
+      </c>
+      <c r="H52" s="3">
         <v>500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>8600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>8400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>500</v>
-      </c>
-      <c r="N52" s="3">
-        <v>100</v>
       </c>
       <c r="O52" s="3">
         <v>100</v>
@@ -4666,10 +4786,10 @@
         <v>100</v>
       </c>
       <c r="W52" s="3">
+        <v>100</v>
+      </c>
+      <c r="X52" s="3">
         <v>200</v>
-      </c>
-      <c r="X52" s="3">
-        <v>100</v>
       </c>
       <c r="Y52" s="3">
         <v>100</v>
@@ -4678,20 +4798,20 @@
         <v>100</v>
       </c>
       <c r="AA52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB52" s="3">
         <v>0</v>
       </c>
       <c r="AC52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD52" s="3">
         <v>300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>100</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF52" s="3" t="s">
         <v>4</v>
       </c>
@@ -4701,8 +4821,11 @@
       <c r="AH52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,95 +4922,98 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E54" s="3">
         <v>26200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>28800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>34900</v>
-      </c>
-      <c r="G54" s="3">
-        <v>29300</v>
       </c>
       <c r="H54" s="3">
         <v>29300</v>
       </c>
       <c r="I54" s="3">
+        <v>29300</v>
+      </c>
+      <c r="J54" s="3">
         <v>31000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>31400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>35600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>40200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>31700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>25000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>30600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>28900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>33900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>25800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>11400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>14900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>14700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>18900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>10000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>15000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>20000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>21500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>24800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>28000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>5600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>7700</v>
       </c>
-      <c r="AE54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF54" s="3" t="s">
         <v>4</v>
       </c>
@@ -4897,8 +5023,11 @@
       <c r="AH54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,95 +5099,96 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E57" s="3">
         <v>2100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1300</v>
-      </c>
-      <c r="H57" s="3">
-        <v>1400</v>
       </c>
       <c r="I57" s="3">
         <v>1400</v>
       </c>
       <c r="J57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K57" s="3">
         <v>1100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1600</v>
-      </c>
-      <c r="N57" s="3">
-        <v>1700</v>
       </c>
       <c r="O57" s="3">
         <v>1700</v>
       </c>
       <c r="P57" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Q57" s="3">
         <v>1800</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>1500</v>
       </c>
       <c r="R57" s="3">
         <v>1500</v>
       </c>
       <c r="S57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="T57" s="3">
         <v>1100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>300</v>
       </c>
-      <c r="AE57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF57" s="3" t="s">
         <v>4</v>
       </c>
@@ -5067,64 +5198,67 @@
       <c r="AH57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E58" s="3">
         <v>8200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>7200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>7400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>7700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>7200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>7300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>800</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>100</v>
       </c>
       <c r="R58" s="3">
         <v>100</v>
       </c>
       <c r="S58" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="T58" s="3">
         <v>400</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>4</v>
+      <c r="U58" s="3">
+        <v>400</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>4</v>
@@ -5141,8 +5275,8 @@
       <c r="Z58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA58" s="3">
-        <v>0</v>
+      <c r="AA58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB58" s="3">
         <v>0</v>
@@ -5165,94 +5299,97 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E59" s="3">
         <v>6200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1600</v>
-      </c>
-      <c r="I59" s="3">
-        <v>2700</v>
       </c>
       <c r="J59" s="3">
         <v>2700</v>
       </c>
       <c r="K59" s="3">
+        <v>2700</v>
+      </c>
+      <c r="L59" s="3">
         <v>1900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>11800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>11900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>13800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>16600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>5100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>900</v>
-      </c>
-      <c r="AA59" s="3">
-        <v>600</v>
       </c>
       <c r="AB59" s="3">
         <v>600</v>
       </c>
       <c r="AC59" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="AD59" s="3">
         <v>300</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>4</v>
+      <c r="AE59" s="3">
+        <v>300</v>
       </c>
       <c r="AF59" s="3" t="s">
         <v>4</v>
@@ -5263,94 +5400,97 @@
       <c r="AH59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E60" s="3">
         <v>16500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>11000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>12000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>10400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>11200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>20700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>14600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>16400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>18200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2900</v>
-      </c>
-      <c r="V60" s="3">
-        <v>2400</v>
       </c>
       <c r="W60" s="3">
         <v>2400</v>
       </c>
       <c r="X60" s="3">
+        <v>2400</v>
+      </c>
+      <c r="Y60" s="3">
         <v>2500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1100</v>
-      </c>
-      <c r="AC60" s="3">
-        <v>600</v>
       </c>
       <c r="AD60" s="3">
         <v>600</v>
       </c>
-      <c r="AE60" s="3" t="s">
-        <v>4</v>
+      <c r="AE60" s="3">
+        <v>600</v>
       </c>
       <c r="AF60" s="3" t="s">
         <v>4</v>
@@ -5361,32 +5501,35 @@
       <c r="AH60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E61" s="3">
         <v>6800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>9000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>11100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>13200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8400</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -5400,23 +5543,23 @@
         <v>0</v>
       </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>7000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>300</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>400</v>
       </c>
       <c r="R61" s="3">
         <v>400</v>
       </c>
       <c r="S61" s="3">
+        <v>400</v>
+      </c>
+      <c r="T61" s="3">
         <v>300</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -5459,35 +5602,38 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>100</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
@@ -5533,21 +5679,21 @@
       <c r="Z62" s="3">
         <v>0</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>4</v>
+      <c r="AA62" s="3">
+        <v>0</v>
       </c>
       <c r="AB62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC62" s="3">
-        <v>0</v>
+      <c r="AC62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE62" s="3">
         <v>6400</v>
       </c>
-      <c r="AE62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF62" s="3" t="s">
         <v>4</v>
       </c>
@@ -5557,8 +5703,11 @@
       <c r="AH62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,95 +6006,98 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E66" s="3">
         <v>24400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>19800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>19100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>18800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>13500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>13800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>11100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>12000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>10400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>11200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>20700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>21600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>16700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>18600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>7200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>7000</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF66" s="3" t="s">
         <v>4</v>
       </c>
@@ -5949,8 +6107,11 @@
       <c r="AH66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,95 +6548,98 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-167500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-156400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-145500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-137500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-130200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-124000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-118200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-112100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-104800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-97600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-90200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-93200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-87600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-82800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-77400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-73200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-68100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-63100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-57700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-52400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-47800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-42400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-36500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-30300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-26000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-22700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-19300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-17100</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF72" s="3" t="s">
         <v>4</v>
       </c>
@@ -6475,8 +6649,11 @@
       <c r="AH72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,95 +6952,98 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E76" s="3">
         <v>1800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>15800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>10500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>15800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>17200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>20300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>23600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>29800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>20500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>9000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>12100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>15300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>18700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>8300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>12300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>11700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>16400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>7600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>12500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>16900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>19700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>23500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>26900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>5100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>700</v>
       </c>
-      <c r="AE76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF76" s="3" t="s">
         <v>4</v>
       </c>
@@ -6867,8 +7053,11 @@
       <c r="AH76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-10900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-8000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-7300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-6200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-5700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-6100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-7300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-7200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-7300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-5600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-4800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-4200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-5100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-5000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-5500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-5200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-4600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-5300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-5900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-6200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-3300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-1100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-1200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,22 +7400,23 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>300</v>
+      </c>
+      <c r="E83" s="3">
         <v>200</v>
-      </c>
-      <c r="E83" s="3">
-        <v>300</v>
       </c>
       <c r="F83" s="3">
         <v>300</v>
       </c>
       <c r="G83" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="H83" s="3">
         <v>100</v>
@@ -7241,7 +7440,7 @@
         <v>100</v>
       </c>
       <c r="O83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P83" s="3">
         <v>0</v>
@@ -7300,8 +7499,11 @@
       <c r="AH83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-9900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-6300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-5800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-4700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-7000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-5400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-6800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-4700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-8200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-5900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-5100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-5300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>5500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-4000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-5900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-4000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-3900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-5100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-5900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-1000</v>
-      </c>
-      <c r="AF89" s="3">
-        <v>-900</v>
       </c>
       <c r="AG89" s="3">
         <v>-900</v>
       </c>
       <c r="AH89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="AI89" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,31 +8144,32 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E91" s="3">
         <v>-100</v>
       </c>
       <c r="F91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G91" s="3">
         <v>-600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-300</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-200</v>
       </c>
       <c r="K91" s="3">
         <v>-200</v>
@@ -7957,34 +8178,34 @@
         <v>-200</v>
       </c>
       <c r="M91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-500</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-300</v>
       </c>
       <c r="P91" s="3">
         <v>-300</v>
       </c>
       <c r="Q91" s="3">
-        <v>-100</v>
+        <v>-300</v>
       </c>
       <c r="R91" s="3">
         <v>-100</v>
       </c>
       <c r="S91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>4</v>
+      <c r="V91" s="3">
+        <v>-100</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>4</v>
@@ -8004,8 +8225,8 @@
       <c r="AB91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC91" s="3">
-        <v>0</v>
+      <c r="AC91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD91" s="3">
         <v>0</v>
@@ -8022,8 +8243,11 @@
       <c r="AH91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,31 +8445,34 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E94" s="3">
         <v>-100</v>
       </c>
       <c r="F94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G94" s="3">
         <v>-1700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-800</v>
       </c>
-      <c r="I94" s="3">
-        <v>-300</v>
-      </c>
       <c r="J94" s="3">
-        <v>-200</v>
+        <v>14700</v>
       </c>
       <c r="K94" s="3">
         <v>-200</v>
@@ -8251,34 +8481,34 @@
         <v>-200</v>
       </c>
       <c r="M94" s="3">
-        <v>-500</v>
+        <v>-200</v>
       </c>
       <c r="N94" s="3">
         <v>-500</v>
       </c>
       <c r="O94" s="3">
-        <v>-300</v>
+        <v>-500</v>
       </c>
       <c r="P94" s="3">
         <v>-300</v>
       </c>
       <c r="Q94" s="3">
-        <v>-100</v>
+        <v>-300</v>
       </c>
       <c r="R94" s="3">
         <v>-100</v>
       </c>
       <c r="S94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U94" s="3">
         <v>-100</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>4</v>
+      <c r="V94" s="3">
+        <v>-100</v>
       </c>
       <c r="W94" s="3" t="s">
         <v>4</v>
@@ -8286,8 +8516,8 @@
       <c r="X94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
+      <c r="Y94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z94" s="3">
         <v>0</v>
@@ -8316,8 +8546,11 @@
       <c r="AH94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,106 +8987,112 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E100" s="3">
         <v>3100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>10800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>5000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>15600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>12300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>7900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>14700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>5500</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>13000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>2800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>100</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>24700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>6800</v>
       </c>
-      <c r="AE100" s="3">
-        <v>0</v>
-      </c>
       <c r="AF100" s="3">
         <v>0</v>
       </c>
       <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="3">
         <v>100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8940,102 +9189,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-6900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-5900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-4100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-5200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>7300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>6000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-5800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>5500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>12700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-3500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-4100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>9100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-5100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-5400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-3500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>22400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>5900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1000</v>
-      </c>
-      <c r="AF102" s="3">
-        <v>-900</v>
       </c>
       <c r="AG102" s="3">
         <v>-900</v>
       </c>
       <c r="AH102" s="3">
+        <v>-900</v>
+      </c>
+      <c r="AI102" s="3">
         <v>1800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EYEN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EYEN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="92">
   <si>
     <t>EYEN</t>
   </si>
@@ -656,151 +656,155 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -816,14 +820,14 @@
       <c r="G8" s="3">
         <v>0</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>4</v>
+      <c r="H8" s="3">
+        <v>0</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="J8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -835,13 +839,13 @@
         <v>0</v>
       </c>
       <c r="N8" s="3">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3">
         <v>10000</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
       <c r="P8" s="3">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="3">
         <v>2000</v>
@@ -849,8 +853,8 @@
       <c r="R8" s="3">
         <v>2000</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>4</v>
+      <c r="S8" s="3">
+        <v>2000</v>
       </c>
       <c r="T8" s="3" t="s">
         <v>4</v>
@@ -864,8 +868,8 @@
       <c r="W8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X8" s="3">
-        <v>0</v>
+      <c r="X8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y8" s="3">
         <v>0</v>
@@ -900,25 +904,28 @@
       <c r="AI8" s="3">
         <v>0</v>
       </c>
+      <c r="AJ8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="E9" s="3">
-        <v>0</v>
+        <v>3400</v>
       </c>
       <c r="F9" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="G9" s="3">
         <v>0</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>4</v>
+      <c r="H9" s="3">
+        <v>0</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>4</v>
@@ -941,8 +948,8 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P9" s="3">
-        <v>800</v>
+      <c r="P9" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q9" s="3">
         <v>800</v>
@@ -950,8 +957,8 @@
       <c r="R9" s="3">
         <v>800</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>4</v>
+      <c r="S9" s="3">
+        <v>800</v>
       </c>
       <c r="T9" s="3" t="s">
         <v>4</v>
@@ -1001,25 +1008,28 @@
       <c r="AI9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>4</v>
+      <c r="D10" s="3">
+        <v>-100</v>
       </c>
       <c r="E10" s="3">
-        <v>0</v>
+        <v>-3300</v>
       </c>
       <c r="F10" s="3">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="G10" s="3">
         <v>0</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>4</v>
+      <c r="H10" s="3">
+        <v>0</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>4</v>
@@ -1042,8 +1052,8 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P10" s="3">
-        <v>1200</v>
+      <c r="P10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q10" s="3">
         <v>1200</v>
@@ -1051,8 +1061,8 @@
       <c r="R10" s="3">
         <v>1200</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>4</v>
+      <c r="S10" s="3">
+        <v>1200</v>
       </c>
       <c r="T10" s="3" t="s">
         <v>4</v>
@@ -1102,8 +1112,11 @@
       <c r="AI10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1139,25 +1152,26 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>4600</v>
+        <v>3300</v>
       </c>
       <c r="E12" s="3">
-        <v>4400</v>
+        <v>4300</v>
       </c>
       <c r="F12" s="3">
-        <v>4100</v>
+        <v>4200</v>
       </c>
       <c r="G12" s="3">
-        <v>3600</v>
+        <v>3500</v>
       </c>
       <c r="H12" s="3">
-        <v>2800</v>
+        <v>3200</v>
       </c>
       <c r="I12" s="3">
         <v>2500</v>
@@ -1166,82 +1180,85 @@
         <v>2300</v>
       </c>
       <c r="K12" s="3">
+        <v>2300</v>
+      </c>
+      <c r="L12" s="3">
         <v>3900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>3700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>4300</v>
-      </c>
-      <c r="R12" s="3">
-        <v>3400</v>
       </c>
       <c r="S12" s="3">
         <v>3400</v>
       </c>
       <c r="T12" s="3">
+        <v>3400</v>
+      </c>
+      <c r="U12" s="3">
         <v>2900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>3600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>3300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>3200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>3600</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>4000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>4100</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>2500</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>2400</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>2100</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>1700</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>600</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>800</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>900</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>1000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,8 +1358,11 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1352,8 +1372,8 @@
       <c r="E14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>4</v>
@@ -1364,27 +1384,27 @@
       <c r="I14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>4</v>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>-500</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1400,8 +1420,8 @@
       <c r="U14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1442,31 +1462,34 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1543,8 +1566,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,160 +1603,164 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E17" s="3">
         <v>11700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>10300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>7500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>7200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>7400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>6200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>6000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>6200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>4</v>
+      <c r="D18" s="3">
+        <v>-7300</v>
       </c>
       <c r="E18" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="F18" s="3">
         <v>-10300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-7500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-6500</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>4</v>
+      <c r="I18" s="3">
+        <v>-6000</v>
       </c>
       <c r="J18" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="K18" s="3">
         <v>-5400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-7200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-7100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-7200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-5500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-5400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-4200</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>4</v>
       </c>
@@ -1743,44 +1773,47 @@
       <c r="W18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X18" s="3">
+      <c r="X18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y18" s="3">
         <v>-5400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-6000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-6200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-4300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-3400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-2200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-1100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-1200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,47 +1849,48 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4</v>
+      <c r="D20" s="3">
+        <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>-1200</v>
       </c>
       <c r="F20" s="3">
+        <v>100</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>300</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="G20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J20" s="3">
-        <v>200</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
@@ -1866,8 +1900,8 @@
       <c r="R20" s="3">
         <v>0</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>4</v>
+      <c r="S20" s="3">
+        <v>0</v>
       </c>
       <c r="T20" s="3" t="s">
         <v>4</v>
@@ -1881,8 +1915,8 @@
       <c r="W20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
+      <c r="X20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y20" s="3">
         <v>0</v>
@@ -1917,59 +1951,62 @@
       <c r="AI20" s="3">
         <v>0</v>
       </c>
+      <c r="AJ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>4</v>
+      <c r="D21" s="3">
+        <v>-7000</v>
       </c>
       <c r="E21" s="3">
-        <v>-10000</v>
+        <v>-10100</v>
       </c>
       <c r="F21" s="3">
-        <v>-7000</v>
+        <v>-10100</v>
       </c>
       <c r="G21" s="3">
-        <v>-6300</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>4</v>
+        <v>-7200</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-5700</v>
       </c>
       <c r="J21" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="K21" s="3">
         <v>-5100</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-7000</v>
       </c>
       <c r="L21" s="3">
         <v>-7000</v>
       </c>
       <c r="M21" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="N21" s="3">
         <v>-7100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-5400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-5300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-4200</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1982,49 +2019,52 @@
       <c r="W21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y21" s="3">
         <v>-5300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-5900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-6200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-4300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-3400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-2100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-1100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-1200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="E22" s="3">
         <v>700</v>
@@ -2036,34 +2076,34 @@
         <v>700</v>
       </c>
       <c r="H22" s="3">
+        <v>700</v>
+      </c>
+      <c r="I22" s="3">
         <v>600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>900</v>
-      </c>
-      <c r="K22" s="3">
-        <v>200</v>
       </c>
       <c r="L22" s="3">
         <v>200</v>
       </c>
       <c r="M22" s="3">
+        <v>200</v>
+      </c>
+      <c r="N22" s="3">
         <v>100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>200</v>
-      </c>
-      <c r="O22" s="3">
-        <v>100</v>
       </c>
       <c r="P22" s="3">
         <v>100</v>
       </c>
       <c r="Q22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2077,8 +2117,8 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>4</v>
+      <c r="V22" s="3">
+        <v>0</v>
       </c>
       <c r="W22" s="3" t="s">
         <v>4</v>
@@ -2095,8 +2135,8 @@
       <c r="AA22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB22" s="3">
-        <v>0</v>
+      <c r="AB22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC22" s="3">
         <v>0</v>
@@ -2119,132 +2159,138 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-11100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-10900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-8000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-7300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-6200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-5700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-6100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-7300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-7200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-7300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-5600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-5400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-4200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-5100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-5000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-5500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-5200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-4600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-5300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-5900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-6200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-4300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-3400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-2200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-1100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-1200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -2321,8 +2367,11 @@
       <c r="AI24" s="3">
         <v>0</v>
       </c>
+      <c r="AJ24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-11100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-10900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-8000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-7300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-6200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-5700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-6100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-7300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-7200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-7300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-5600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-5400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-4200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-5100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-5000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-5500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-5200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-4600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-5300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-5900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-6200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-4300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-3400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-1100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-1200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-11100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-10900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-8000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-7300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-6200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-5700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-6100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-7300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-7200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-7300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-5600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-5400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-4200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-5100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-5000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-5500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-5200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-4600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-5300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-5900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-6200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-4300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-3400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-2200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-1100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-1200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2826,8 +2887,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,47 +3095,50 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>4</v>
+      <c r="D32" s="3">
+        <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="F32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I32" s="3">
+        <v>100</v>
+      </c>
+      <c r="J32" s="3">
+        <v>100</v>
+      </c>
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="G32" s="3">
-        <v>100</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
@@ -3078,8 +3148,8 @@
       <c r="R32" s="3">
         <v>0</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>4</v>
+      <c r="S32" s="3">
+        <v>0</v>
       </c>
       <c r="T32" s="3" t="s">
         <v>4</v>
@@ -3093,8 +3163,8 @@
       <c r="W32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
+      <c r="X32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y32" s="3">
         <v>0</v>
@@ -3129,109 +3199,115 @@
       <c r="AI32" s="3">
         <v>0</v>
       </c>
+      <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-11100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-10900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-8000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-7300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-6200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-5700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-6100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-7300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-7200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-7300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-5600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-5400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-4200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-5100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-5000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-5500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-5200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-4600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-5300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-5900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-6200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-4300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-3400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-2200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-1100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-1200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-11100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-10900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-8000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-7300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-6200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-5700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-6100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-7300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-7200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-7300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-5600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-5400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-4200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-5100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-5000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-5500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-5200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-4600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-5300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-5900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-6200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-4300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-3400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-2200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-1100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-1200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,98 +3698,99 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E41" s="3">
         <v>2300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>8000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>14800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>20700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>17500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>18500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>22900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>17400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>21500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>26700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>19500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>13500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>27200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>24900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>28400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>22900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>10200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>13700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>14200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>18300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>9200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>14300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>19700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>21000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>24600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>27600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>5200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>7400</v>
       </c>
-      <c r="AF41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG41" s="3" t="s">
         <v>4</v>
       </c>
@@ -3713,8 +3800,11 @@
       <c r="AI41" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ41" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3748,14 +3838,14 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>4</v>
+      <c r="N42" s="3">
+        <v>0</v>
       </c>
       <c r="O42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
+      <c r="P42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q42" s="3">
         <v>0</v>
@@ -3814,8 +3904,11 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3823,55 +3916,55 @@
         <v>400</v>
       </c>
       <c r="E43" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="F43" s="3">
         <v>600</v>
       </c>
       <c r="G43" s="3">
+        <v>600</v>
+      </c>
+      <c r="H43" s="3">
         <v>900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1300</v>
-      </c>
-      <c r="P43" s="3">
-        <v>1200</v>
       </c>
       <c r="Q43" s="3">
         <v>1200</v>
       </c>
       <c r="R43" s="3">
+        <v>1200</v>
+      </c>
+      <c r="S43" s="3">
         <v>3100</v>
-      </c>
-      <c r="S43" s="3">
-        <v>200</v>
       </c>
       <c r="T43" s="3">
         <v>200</v>
       </c>
       <c r="U43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="V43" s="3">
         <v>100</v>
@@ -3885,8 +3978,8 @@
       <c r="Y43" s="3">
         <v>100</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>4</v>
+      <c r="Z43" s="3">
+        <v>100</v>
       </c>
       <c r="AA43" s="3" t="s">
         <v>4</v>
@@ -3897,8 +3990,8 @@
       <c r="AC43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD43" s="3">
-        <v>0</v>
+      <c r="AD43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE43" s="3">
         <v>0</v>
@@ -3915,25 +4008,28 @@
       <c r="AI43" s="3">
         <v>0</v>
       </c>
+      <c r="AJ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E44" s="3">
         <v>3100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3500</v>
-      </c>
-      <c r="F44" s="3">
-        <v>100</v>
       </c>
       <c r="G44" s="3">
         <v>100</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>4</v>
+      <c r="H44" s="3">
+        <v>100</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>4</v>
@@ -3950,8 +4046,8 @@
       <c r="M44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N44" s="3">
-        <v>0</v>
+      <c r="N44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O44" s="3">
         <v>0</v>
@@ -4016,98 +4112,101 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="E45" s="3">
-        <v>2400</v>
+        <v>500</v>
       </c>
       <c r="F45" s="3">
-        <v>5100</v>
+        <v>1100</v>
       </c>
       <c r="G45" s="3">
-        <v>4900</v>
+        <v>4700</v>
       </c>
       <c r="H45" s="3">
-        <v>4700</v>
+        <v>3800</v>
       </c>
       <c r="I45" s="3">
-        <v>4800</v>
+        <v>3700</v>
       </c>
       <c r="J45" s="3">
+        <v>3500</v>
+      </c>
+      <c r="K45" s="3">
         <v>2900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>10600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>8300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>8700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1100</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>1900</v>
       </c>
       <c r="R45" s="3">
         <v>1900</v>
       </c>
       <c r="S45" s="3">
+        <v>1900</v>
+      </c>
+      <c r="T45" s="3">
         <v>2300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>300</v>
-      </c>
-      <c r="X45" s="3">
-        <v>500</v>
       </c>
       <c r="Y45" s="3">
         <v>500</v>
       </c>
       <c r="Z45" s="3">
+        <v>500</v>
+      </c>
+      <c r="AA45" s="3">
         <v>100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>400</v>
       </c>
-      <c r="AD45" s="3">
-        <v>0</v>
-      </c>
       <c r="AE45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF45" s="3">
         <v>100</v>
       </c>
-      <c r="AF45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG45" s="3" t="s">
         <v>4</v>
       </c>
@@ -4117,98 +4216,101 @@
       <c r="AI45" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ45" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E46" s="3">
         <v>7300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>14500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>20700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>26500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>23300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>24900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>27600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>29400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>25600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>30400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>29900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>23500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>29500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>28000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>33400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>25400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>11000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>14500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>14300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>18700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>9800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>14900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>19900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>21300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>24800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>28000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>5300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>7500</v>
       </c>
-      <c r="AF46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG46" s="3" t="s">
         <v>4</v>
       </c>
@@ -4218,31 +4320,34 @@
       <c r="AI46" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ46" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4253,14 +4358,14 @@
       <c r="M47" s="3">
         <v>0</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>4</v>
+      <c r="N47" s="3">
+        <v>0</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -4319,74 +4424,77 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E48" s="3">
         <v>4500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1300</v>
-      </c>
-      <c r="L48" s="3">
-        <v>1400</v>
       </c>
       <c r="M48" s="3">
         <v>1400</v>
       </c>
       <c r="N48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="O48" s="3">
         <v>1300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>700</v>
-      </c>
-      <c r="R48" s="3">
-        <v>400</v>
       </c>
       <c r="S48" s="3">
         <v>400</v>
       </c>
       <c r="T48" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="U48" s="3">
         <v>300</v>
       </c>
       <c r="V48" s="3">
+        <v>300</v>
+      </c>
+      <c r="W48" s="3">
         <v>200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>100</v>
       </c>
-      <c r="X48" s="3">
-        <v>0</v>
-      </c>
       <c r="Y48" s="3">
         <v>0</v>
       </c>
@@ -4408,8 +4516,8 @@
       <c r="AE48" s="3">
         <v>0</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>4</v>
+      <c r="AF48" s="3">
+        <v>0</v>
       </c>
       <c r="AG48" s="3" t="s">
         <v>4</v>
@@ -4420,8 +4528,11 @@
       <c r="AI48" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ48" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4432,19 +4543,19 @@
         <v>6100</v>
       </c>
       <c r="F49" s="3">
-        <v>2100</v>
+        <v>6100</v>
       </c>
       <c r="G49" s="3">
         <v>2100</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>4</v>
+      <c r="H49" s="3">
+        <v>2100</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
+        <v>0</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>4</v>
@@ -4455,8 +4566,8 @@
       <c r="M49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
+      <c r="N49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O49" s="3">
         <v>0</v>
@@ -4521,8 +4632,11 @@
       <c r="AI49" s="3">
         <v>0</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,16 +4840,19 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="E52" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="F52" s="3">
         <v>900</v>
@@ -4741,28 +4861,28 @@
         <v>900</v>
       </c>
       <c r="H52" s="3">
+        <v>900</v>
+      </c>
+      <c r="I52" s="3">
         <v>500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>8600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>8400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>500</v>
-      </c>
-      <c r="O52" s="3">
-        <v>100</v>
       </c>
       <c r="P52" s="3">
         <v>100</v>
@@ -4789,10 +4909,10 @@
         <v>100</v>
       </c>
       <c r="X52" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y52" s="3">
         <v>200</v>
-      </c>
-      <c r="Y52" s="3">
-        <v>100</v>
       </c>
       <c r="Z52" s="3">
         <v>100</v>
@@ -4801,20 +4921,20 @@
         <v>100</v>
       </c>
       <c r="AB52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC52" s="3">
         <v>0</v>
       </c>
       <c r="AD52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE52" s="3">
         <v>300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>100</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG52" s="3" t="s">
         <v>4</v>
       </c>
@@ -4824,8 +4944,11 @@
       <c r="AI52" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ52" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,98 +5048,101 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>22800</v>
+      </c>
+      <c r="E54" s="3">
         <v>19000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>26200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>28800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>34900</v>
-      </c>
-      <c r="H54" s="3">
-        <v>29300</v>
       </c>
       <c r="I54" s="3">
         <v>29300</v>
       </c>
       <c r="J54" s="3">
+        <v>29300</v>
+      </c>
+      <c r="K54" s="3">
         <v>31000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>31400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>35600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>40200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>31700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>25000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>30600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>28900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>33900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>25800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>11400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>14900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>14700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>18900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>10000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>15000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>20000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>21500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>24800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>28000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>5600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>7700</v>
       </c>
-      <c r="AF54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG54" s="3" t="s">
         <v>4</v>
       </c>
@@ -5026,8 +5152,11 @@
       <c r="AI54" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ54" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,98 +5230,99 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E57" s="3">
         <v>1400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1300</v>
-      </c>
-      <c r="I57" s="3">
-        <v>1400</v>
       </c>
       <c r="J57" s="3">
         <v>1400</v>
       </c>
       <c r="K57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="L57" s="3">
         <v>1100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1600</v>
-      </c>
-      <c r="O57" s="3">
-        <v>1700</v>
       </c>
       <c r="P57" s="3">
         <v>1700</v>
       </c>
       <c r="Q57" s="3">
+        <v>1700</v>
+      </c>
+      <c r="R57" s="3">
         <v>1800</v>
-      </c>
-      <c r="R57" s="3">
-        <v>1500</v>
       </c>
       <c r="S57" s="3">
         <v>1500</v>
       </c>
       <c r="T57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="U57" s="3">
         <v>1100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>300</v>
       </c>
-      <c r="AF57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG57" s="3" t="s">
         <v>4</v>
       </c>
@@ -5201,67 +5332,70 @@
       <c r="AI57" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ57" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>9500</v>
+        <v>10000</v>
       </c>
       <c r="E58" s="3">
-        <v>8200</v>
+        <v>10100</v>
       </c>
       <c r="F58" s="3">
-        <v>5300</v>
+        <v>8700</v>
       </c>
       <c r="G58" s="3">
-        <v>3000</v>
+        <v>5800</v>
       </c>
       <c r="H58" s="3">
-        <v>900</v>
+        <v>3500</v>
       </c>
       <c r="I58" s="3">
-        <v>1900</v>
+        <v>1400</v>
       </c>
       <c r="J58" s="3">
+        <v>2400</v>
+      </c>
+      <c r="K58" s="3">
         <v>300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>7200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>7400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>7700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>7200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>7300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>800</v>
-      </c>
-      <c r="R58" s="3">
-        <v>100</v>
       </c>
       <c r="S58" s="3">
         <v>100</v>
       </c>
       <c r="T58" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="U58" s="3">
         <v>400</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>4</v>
+      <c r="V58" s="3">
+        <v>400</v>
       </c>
       <c r="W58" s="3" t="s">
         <v>4</v>
@@ -5278,8 +5412,8 @@
       <c r="AA58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB58" s="3">
-        <v>0</v>
+      <c r="AB58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC58" s="3">
         <v>0</v>
@@ -5302,97 +5436,100 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4900</v>
+        <v>2300</v>
       </c>
       <c r="E59" s="3">
-        <v>6200</v>
+        <v>300</v>
       </c>
       <c r="F59" s="3">
-        <v>2400</v>
+        <v>4500</v>
       </c>
       <c r="G59" s="3">
-        <v>2100</v>
+        <v>100</v>
       </c>
       <c r="H59" s="3">
-        <v>1800</v>
+        <v>200</v>
       </c>
       <c r="I59" s="3">
-        <v>1600</v>
+        <v>100</v>
       </c>
       <c r="J59" s="3">
-        <v>2700</v>
+        <v>0</v>
       </c>
       <c r="K59" s="3">
         <v>2700</v>
       </c>
       <c r="L59" s="3">
+        <v>2700</v>
+      </c>
+      <c r="M59" s="3">
         <v>1900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>11800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>11900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>13800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>16600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>5100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>900</v>
-      </c>
-      <c r="AB59" s="3">
-        <v>600</v>
       </c>
       <c r="AC59" s="3">
         <v>600</v>
       </c>
       <c r="AD59" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="AE59" s="3">
         <v>300</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>4</v>
+      <c r="AF59" s="3">
+        <v>300</v>
       </c>
       <c r="AG59" s="3" t="s">
         <v>4</v>
@@ -5403,8 +5540,11 @@
       <c r="AI59" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ59" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5412,88 +5552,88 @@
         <v>15800</v>
       </c>
       <c r="E60" s="3">
+        <v>15800</v>
+      </c>
+      <c r="F60" s="3">
         <v>16500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>9500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>11000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>12000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>10400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>11200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>20700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>14600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>16400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>18200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>6700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2900</v>
-      </c>
-      <c r="W60" s="3">
-        <v>2400</v>
       </c>
       <c r="X60" s="3">
         <v>2400</v>
       </c>
       <c r="Y60" s="3">
+        <v>2400</v>
+      </c>
+      <c r="Z60" s="3">
         <v>2500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1100</v>
-      </c>
-      <c r="AD60" s="3">
-        <v>600</v>
       </c>
       <c r="AE60" s="3">
         <v>600</v>
       </c>
-      <c r="AF60" s="3" t="s">
-        <v>4</v>
+      <c r="AF60" s="3">
+        <v>600</v>
       </c>
       <c r="AG60" s="3" t="s">
         <v>4</v>
@@ -5504,35 +5644,38 @@
       <c r="AI60" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ60" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>4500</v>
+        <v>3000</v>
       </c>
       <c r="E61" s="3">
-        <v>6800</v>
+        <v>5500</v>
       </c>
       <c r="F61" s="3">
-        <v>9000</v>
+        <v>7900</v>
       </c>
       <c r="G61" s="3">
-        <v>11100</v>
+        <v>10200</v>
       </c>
       <c r="H61" s="3">
-        <v>13200</v>
+        <v>12500</v>
       </c>
       <c r="I61" s="3">
-        <v>7500</v>
+        <v>14800</v>
       </c>
       <c r="J61" s="3">
+        <v>8600</v>
+      </c>
+      <c r="K61" s="3">
         <v>8400</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -5546,23 +5689,23 @@
         <v>0</v>
       </c>
       <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
         <v>7000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>300</v>
-      </c>
-      <c r="R61" s="3">
-        <v>400</v>
       </c>
       <c r="S61" s="3">
         <v>400</v>
       </c>
       <c r="T61" s="3">
+        <v>400</v>
+      </c>
+      <c r="U61" s="3">
         <v>300</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -5605,38 +5748,41 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1000</v>
-      </c>
-      <c r="E62" s="3">
-        <v>1100</v>
-      </c>
-      <c r="F62" s="3">
-        <v>1300</v>
-      </c>
-      <c r="G62" s="3">
-        <v>1400</v>
-      </c>
-      <c r="H62" s="3">
-        <v>1600</v>
-      </c>
-      <c r="I62" s="3">
-        <v>1100</v>
-      </c>
-      <c r="J62" s="3">
+        <v>300</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K62" s="3">
         <v>900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>100</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
@@ -5682,21 +5828,21 @@
       <c r="AA62" s="3">
         <v>0</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>4</v>
+      <c r="AB62" s="3">
+        <v>0</v>
       </c>
       <c r="AC62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD62" s="3">
-        <v>0</v>
+      <c r="AD62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF62" s="3">
         <v>6400</v>
       </c>
-      <c r="AF62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG62" s="3" t="s">
         <v>4</v>
       </c>
@@ -5706,8 +5852,11 @@
       <c r="AI62" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ62" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,98 +6164,101 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E66" s="3">
         <v>21400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>24400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>19800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>19100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>18800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>13500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>13800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>11100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>12000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>10400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>11200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>20700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>21600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>16700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>18600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>7200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>7000</v>
       </c>
-      <c r="AF66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG66" s="3" t="s">
         <v>4</v>
       </c>
@@ -6110,8 +6268,11 @@
       <c r="AI66" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ66" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,98 +6722,101 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-175400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-167500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-156400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-145500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-137500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-130200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-124000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-118200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-112100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-104800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-97600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-90200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-93200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-87600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-82800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-77400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-73200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-68100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-63100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-57700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-52400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-47800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-42400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-36500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-30300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-26000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-22700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-19300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-17100</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG72" s="3" t="s">
         <v>4</v>
       </c>
@@ -6652,8 +6826,11 @@
       <c r="AI72" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ72" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,98 +7138,101 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E76" s="3">
         <v>-2400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>15800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>10500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>15800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>17200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>20300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>23600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>29800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>20500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>9000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>12100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>15300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>18700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>8300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>12300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>11700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>16400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>7600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>12500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>16900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>19700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>23500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>26900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>5100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>700</v>
       </c>
-      <c r="AF76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG76" s="3" t="s">
         <v>4</v>
       </c>
@@ -7056,8 +7242,11 @@
       <c r="AI76" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ76" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-11100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-10900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-8000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-7300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-6200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-5700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-6100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-7300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-7200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-7300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-5600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-5400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-4200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-5100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-5000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-5500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-5200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-4600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-5300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-5900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-6200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-4300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-3400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-2200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-1100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-1200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,8 +7599,9 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7410,22 +7609,22 @@
         <v>300</v>
       </c>
       <c r="E83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F83" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="G83" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H83" s="3">
         <v>100</v>
       </c>
       <c r="I83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K83" s="3">
         <v>100</v>
@@ -7443,7 +7642,7 @@
         <v>100</v>
       </c>
       <c r="P83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q83" s="3">
         <v>0</v>
@@ -7502,8 +7701,11 @@
       <c r="AI83" s="3">
         <v>0</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-8200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-9900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-6300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-5800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-4700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-7000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-5400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-6800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-4700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-8200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-5900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-5100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-4600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>5500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-4000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-5900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-4000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-3900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-5900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-3000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-1000</v>
-      </c>
-      <c r="AG89" s="3">
-        <v>-900</v>
       </c>
       <c r="AH89" s="3">
         <v>-900</v>
       </c>
       <c r="AI89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="AJ89" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,8 +8365,9 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8154,25 +8375,25 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F91" s="3">
         <v>-100</v>
       </c>
       <c r="G91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H91" s="3">
         <v>-600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-300</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-200</v>
       </c>
       <c r="L91" s="3">
         <v>-200</v>
@@ -8181,34 +8402,34 @@
         <v>-200</v>
       </c>
       <c r="N91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-500</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-300</v>
       </c>
       <c r="Q91" s="3">
         <v>-300</v>
       </c>
       <c r="R91" s="3">
-        <v>-100</v>
+        <v>-300</v>
       </c>
       <c r="S91" s="3">
         <v>-100</v>
       </c>
       <c r="T91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>4</v>
+      <c r="W91" s="3">
+        <v>-100</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>4</v>
@@ -8228,8 +8449,8 @@
       <c r="AC91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD91" s="3">
-        <v>0</v>
+      <c r="AD91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE91" s="3">
         <v>0</v>
@@ -8246,8 +8467,11 @@
       <c r="AI91" s="3">
         <v>0</v>
       </c>
+      <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,8 +8675,11 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8457,25 +8687,25 @@
         <v>0</v>
       </c>
       <c r="E94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F94" s="3">
         <v>-100</v>
       </c>
       <c r="G94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H94" s="3">
         <v>-1700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>14700</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-200</v>
       </c>
       <c r="L94" s="3">
         <v>-200</v>
@@ -8484,34 +8714,34 @@
         <v>-200</v>
       </c>
       <c r="N94" s="3">
-        <v>-500</v>
+        <v>-200</v>
       </c>
       <c r="O94" s="3">
         <v>-500</v>
       </c>
       <c r="P94" s="3">
-        <v>-300</v>
+        <v>-500</v>
       </c>
       <c r="Q94" s="3">
         <v>-300</v>
       </c>
       <c r="R94" s="3">
-        <v>-100</v>
+        <v>-300</v>
       </c>
       <c r="S94" s="3">
         <v>-100</v>
       </c>
       <c r="T94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V94" s="3">
         <v>-100</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>4</v>
+      <c r="W94" s="3">
+        <v>-100</v>
       </c>
       <c r="X94" s="3" t="s">
         <v>4</v>
@@ -8519,8 +8749,8 @@
       <c r="Y94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
+      <c r="Z94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA94" s="3">
         <v>0</v>
@@ -8549,8 +8779,11 @@
       <c r="AI94" s="3">
         <v>0</v>
       </c>
+      <c r="AJ94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,31 +8819,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8687,8 +8921,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,132 +9233,138 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E100" s="3">
         <v>2500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>10800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>5000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>3300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>15600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>12300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>7900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>14700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>5500</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>13000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>2800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>100</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>24700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>6800</v>
       </c>
-      <c r="AF100" s="3">
-        <v>0</v>
-      </c>
       <c r="AG100" s="3">
         <v>0</v>
       </c>
       <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI100" s="3">
         <v>100</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -9192,105 +9441,111 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-5700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-6900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-5900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-4100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-5200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>7300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>6000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-5800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-3500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>5500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>12700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-3500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-4100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>9100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-5400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-3500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-3000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>22400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-2200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>5900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1000</v>
-      </c>
-      <c r="AG102" s="3">
-        <v>-900</v>
       </c>
       <c r="AH102" s="3">
         <v>-900</v>
       </c>
       <c r="AI102" s="3">
+        <v>-900</v>
+      </c>
+      <c r="AJ102" s="3">
         <v>1800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EYEN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EYEN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="92">
   <si>
     <t>EYEN</t>
   </si>
@@ -656,155 +656,162 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -823,17 +830,17 @@
       <c r="H8" s="3">
         <v>0</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3">
-        <v>0</v>
+      <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -842,25 +849,25 @@
         <v>0</v>
       </c>
       <c r="O8" s="3">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3">
         <v>10000</v>
       </c>
-      <c r="P8" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>2000</v>
-      </c>
       <c r="R8" s="3">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="S8" s="3">
         <v>2000</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U8" s="3" t="s">
-        <v>4</v>
+      <c r="T8" s="3">
+        <v>2000</v>
+      </c>
+      <c r="U8" s="3">
+        <v>2000</v>
       </c>
       <c r="V8" s="3" t="s">
         <v>4</v>
@@ -871,11 +878,11 @@
       <c r="X8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y8" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="3">
-        <v>0</v>
+      <c r="Y8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA8" s="3">
         <v>0</v>
@@ -907,31 +914,37 @@
       <c r="AJ8" s="3">
         <v>0</v>
       </c>
+      <c r="AK8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F9" s="3">
         <v>100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>3400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>2000</v>
       </c>
-      <c r="G9" s="3">
-        <v>0</v>
-      </c>
-      <c r="H9" s="3">
-        <v>0</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>4</v>
+      <c r="I9" s="3">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3">
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>4</v>
@@ -951,20 +964,20 @@
       <c r="P9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q9" s="3">
-        <v>800</v>
-      </c>
-      <c r="R9" s="3">
-        <v>800</v>
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S9" s="3">
         <v>800</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U9" s="3" t="s">
-        <v>4</v>
+      <c r="T9" s="3">
+        <v>800</v>
+      </c>
+      <c r="U9" s="3">
+        <v>800</v>
       </c>
       <c r="V9" s="3" t="s">
         <v>4</v>
@@ -1011,31 +1024,37 @@
       <c r="AJ9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="F10" s="3">
         <v>-100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>-3300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>-2000</v>
       </c>
-      <c r="G10" s="3">
-        <v>0</v>
-      </c>
-      <c r="H10" s="3">
-        <v>0</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>4</v>
+      <c r="I10" s="3">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>4</v>
@@ -1055,20 +1074,20 @@
       <c r="P10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q10" s="3">
-        <v>1200</v>
-      </c>
-      <c r="R10" s="3">
-        <v>1200</v>
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S10" s="3">
         <v>1200</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U10" s="3" t="s">
-        <v>4</v>
+      <c r="T10" s="3">
+        <v>1200</v>
+      </c>
+      <c r="U10" s="3">
+        <v>1200</v>
       </c>
       <c r="V10" s="3" t="s">
         <v>4</v>
@@ -1115,8 +1134,14 @@
       <c r="AJ10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1153,112 +1178,120 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>700</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F12" s="3">
         <v>3300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>4300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>4200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>3500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>3200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>2500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>2300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>2300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>3900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>3600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>3700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>3200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>3600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>3700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>4300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>3400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>3400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>2900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>3600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>3300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>3200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>3600</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>4000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>4100</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>2500</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>2400</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>2100</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>1700</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>600</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AI12" s="3">
         <v>800</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AJ12" s="3">
         <v>900</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AK12" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AL12" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,16 +1394,22 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
+      <c r="D14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E14" s="3">
+        <v>10000</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>4</v>
@@ -1387,30 +1426,30 @@
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>-500</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1423,11 +1462,11 @@
       <c r="V14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1465,8 +1504,14 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1477,26 +1522,26 @@
         <v>300</v>
       </c>
       <c r="F15" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G15" s="3">
         <v>300</v>
       </c>
       <c r="H15" s="3">
+        <v>200</v>
+      </c>
+      <c r="I15" s="3">
         <v>300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
+        <v>300</v>
+      </c>
+      <c r="K15" s="3">
         <v>100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>100</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1569,8 +1614,14 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,169 +1655,177 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>8300</v>
+      </c>
+      <c r="F17" s="3">
         <v>7300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>11700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>10300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>7500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>6500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>6000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>5500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>5400</v>
-      </c>
-      <c r="L17" s="3">
-        <v>7200</v>
-      </c>
-      <c r="M17" s="3">
-        <v>7100</v>
       </c>
       <c r="N17" s="3">
         <v>7200</v>
       </c>
       <c r="O17" s="3">
+        <v>7100</v>
+      </c>
+      <c r="P17" s="3">
+        <v>7200</v>
+      </c>
+      <c r="Q17" s="3">
         <v>6900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>5500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>6800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>7400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>6200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>5100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>5000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>5500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>5300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>4700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>5400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>6000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>6200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>4300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>3300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>3400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>2200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>1000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>1100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>1200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="F18" s="3">
         <v>-7300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-11700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-10300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-7500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-6500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-6000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-5500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-5400</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-7200</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-7100</v>
       </c>
       <c r="N18" s="3">
         <v>-7200</v>
       </c>
       <c r="O18" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="P18" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="Q18" s="3">
         <v>3100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-4800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-5400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-4200</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>4</v>
       </c>
@@ -1776,44 +1835,50 @@
       <c r="X18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Y18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA18" s="3">
         <v>-5400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-6000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-6200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-4300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-3300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-3400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>-900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>-1200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,8 +1915,10 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1859,55 +1926,55 @@
         <v>0</v>
       </c>
       <c r="E20" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>-1200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U20" s="3" t="s">
-        <v>4</v>
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
+        <v>0</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>4</v>
@@ -1918,11 +1985,11 @@
       <c r="X20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>0</v>
+      <c r="Y20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA20" s="3">
         <v>0</v>
@@ -1954,65 +2021,71 @@
       <c r="AJ20" s="3">
         <v>0</v>
       </c>
+      <c r="AK20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="F21" s="3">
         <v>-7000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-10100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-10100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-7200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-6500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-5700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-5300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-5100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-7000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-7000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-7100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>3200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-4700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-5300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-4200</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>4</v>
       </c>
@@ -2022,44 +2095,50 @@
       <c r="X21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA21" s="3">
         <v>-5300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-5900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-6200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-4300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>-3300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>-3400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>-2100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>-900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>-1200</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2067,10 +2146,10 @@
         <v>600</v>
       </c>
       <c r="E22" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="F22" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="G22" s="3">
         <v>700</v>
@@ -2079,22 +2158,22 @@
         <v>700</v>
       </c>
       <c r="I22" s="3">
+        <v>700</v>
+      </c>
+      <c r="J22" s="3">
+        <v>700</v>
+      </c>
+      <c r="K22" s="3">
         <v>600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>200</v>
-      </c>
-      <c r="M22" s="3">
-        <v>200</v>
-      </c>
-      <c r="N22" s="3">
-        <v>100</v>
       </c>
       <c r="O22" s="3">
         <v>200</v>
@@ -2103,13 +2182,13 @@
         <v>100</v>
       </c>
       <c r="Q22" s="3">
+        <v>200</v>
+      </c>
+      <c r="R22" s="3">
         <v>100</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
       <c r="S22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T22" s="3">
         <v>0</v>
@@ -2120,11 +2199,11 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X22" s="3" t="s">
-        <v>4</v>
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3">
+        <v>0</v>
       </c>
       <c r="Y22" s="3" t="s">
         <v>4</v>
@@ -2138,11 +2217,11 @@
       <c r="AB22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>0</v>
+      <c r="AC22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE22" s="3">
         <v>0</v>
@@ -2162,112 +2241,124 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="F23" s="3">
         <v>-7900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-11100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-10900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-8000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-7300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-6200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-5700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-6100</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-7300</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-7200</v>
       </c>
       <c r="N23" s="3">
         <v>-7300</v>
       </c>
       <c r="O23" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="P23" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="Q23" s="3">
         <v>3000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-4800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-5400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-4200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-5100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-5000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-5500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-5200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-4600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-5300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-5900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-6200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-4300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-3300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-3400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>-1200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2292,11 +2383,11 @@
       <c r="J24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -2370,8 +2461,14 @@
       <c r="AJ24" s="3">
         <v>0</v>
       </c>
+      <c r="AK24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2571,234 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="F26" s="3">
         <v>-7900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-11100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-10900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-8000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-7300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-6200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-5700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-6100</v>
-      </c>
-      <c r="L26" s="3">
-        <v>-7300</v>
-      </c>
-      <c r="M26" s="3">
-        <v>-7200</v>
       </c>
       <c r="N26" s="3">
         <v>-7300</v>
       </c>
       <c r="O26" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="P26" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="Q26" s="3">
         <v>3000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-4800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-5400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-4200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-5100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-5000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-5500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-5200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-4600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-5300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-5900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-6200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-4300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-3300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-3400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>-1200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="F27" s="3">
         <v>-7900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-11100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-10900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-8000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-7300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-6200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-5700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-6100</v>
-      </c>
-      <c r="L27" s="3">
-        <v>-7300</v>
-      </c>
-      <c r="M27" s="3">
-        <v>-7200</v>
       </c>
       <c r="N27" s="3">
         <v>-7300</v>
       </c>
       <c r="O27" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="P27" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="Q27" s="3">
         <v>3000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-4800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-5400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-4200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-5100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-5000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-5500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-5200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-4600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-5300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-5900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-6200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-4300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-3300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-3400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>-1200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2901,14 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2890,8 +3011,14 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3121,14 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,8 +3231,14 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3107,55 +3246,55 @@
         <v>0</v>
       </c>
       <c r="E32" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>1200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>-300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U32" s="3" t="s">
-        <v>4</v>
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
+        <v>0</v>
       </c>
       <c r="V32" s="3" t="s">
         <v>4</v>
@@ -3166,11 +3305,11 @@
       <c r="X32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>0</v>
+      <c r="Y32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA32" s="3">
         <v>0</v>
@@ -3202,112 +3341,124 @@
       <c r="AJ32" s="3">
         <v>0</v>
       </c>
+      <c r="AK32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="F33" s="3">
         <v>-7900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-11100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-10900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-8000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-7300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-6200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-5700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-6100</v>
-      </c>
-      <c r="L33" s="3">
-        <v>-7300</v>
-      </c>
-      <c r="M33" s="3">
-        <v>-7200</v>
       </c>
       <c r="N33" s="3">
         <v>-7300</v>
       </c>
       <c r="O33" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="P33" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="Q33" s="3">
         <v>3000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-4800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-5400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-4200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-5100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-5000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-5500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-5200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-4600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-5300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-5900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-6200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-4300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-3300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-3400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>-1200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3561,239 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="F35" s="3">
         <v>-7900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-11100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-10900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-8000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-7300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-6200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-5700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-6100</v>
-      </c>
-      <c r="L35" s="3">
-        <v>-7300</v>
-      </c>
-      <c r="M35" s="3">
-        <v>-7200</v>
       </c>
       <c r="N35" s="3">
         <v>-7300</v>
       </c>
       <c r="O35" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="P35" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="Q35" s="3">
         <v>3000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-4800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-5400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-4200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-5100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-5000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-5500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-5200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-4600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-5300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-5900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-6200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-4300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-3300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-3400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>-1200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3830,10 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,112 +3870,120 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F41" s="3">
         <v>7200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>2300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>8000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>14800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>20700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>17500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>18500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>22900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>17400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>21500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>26700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>19500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>13500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>27200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>24900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>28400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>22900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>10200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>13700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>14200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>18300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>9200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>14300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>19700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>21000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>24600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>27600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>5200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>7400</v>
       </c>
-      <c r="AG41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI41" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ41" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL41" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3841,17 +4020,17 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
-      <c r="R42" s="3">
-        <v>0</v>
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S42" s="3">
         <v>0</v>
@@ -3907,70 +4086,76 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3">
+        <v>300</v>
+      </c>
+      <c r="F43" s="3">
         <v>400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>1900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>2100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>1300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>1200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>1200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>3100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>200</v>
-      </c>
-      <c r="V43" s="3">
-        <v>100</v>
-      </c>
-      <c r="W43" s="3">
-        <v>100</v>
       </c>
       <c r="X43" s="3">
         <v>100</v>
@@ -3981,11 +4166,11 @@
       <c r="Z43" s="3">
         <v>100</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB43" s="3" t="s">
-        <v>4</v>
+      <c r="AA43" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB43" s="3">
+        <v>100</v>
       </c>
       <c r="AC43" s="3" t="s">
         <v>4</v>
@@ -3993,11 +4178,11 @@
       <c r="AD43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE43" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF43" s="3">
-        <v>0</v>
+      <c r="AE43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AG43" s="3">
         <v>0</v>
@@ -4011,32 +4196,38 @@
       <c r="AJ43" s="3">
         <v>0</v>
       </c>
+      <c r="AK43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3">
         <v>3000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>3100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>3500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>100</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
@@ -4049,11 +4240,11 @@
       <c r="N44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -4115,216 +4306,234 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3">
+        <v>100</v>
+      </c>
+      <c r="F45" s="3">
         <v>500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>1100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>4700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>3800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>3700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>3500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>2900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>10600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>2800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>1800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>8300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>8700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>1100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>1900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>1900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>2300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>400</v>
       </c>
-      <c r="AE45" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH45" s="3">
         <v>100</v>
       </c>
-      <c r="AG45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI45" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ45" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL45" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F46" s="3">
         <v>11700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>7300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>14500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>20700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>26500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>23300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>24900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>27600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>29400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>25600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>30400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>29900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>23500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>29500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>28000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>33400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>25400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>11000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>14500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>14300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>18700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>9800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>14900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>19900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>21300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>24800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>28000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>5300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>7500</v>
       </c>
-      <c r="AG46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI46" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ46" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL46" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4349,11 +4558,11 @@
       <c r="J47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -4361,17 +4570,17 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
-      <c r="R47" s="3">
-        <v>0</v>
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S47" s="3">
         <v>0</v>
@@ -4427,80 +4636,86 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>600</v>
+      </c>
+      <c r="E48" s="3">
+        <v>700</v>
+      </c>
+      <c r="F48" s="3">
         <v>4000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>4500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>4700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>5000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>5300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>5600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>3700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>2600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>1300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>1400</v>
-      </c>
-      <c r="N48" s="3">
-        <v>1400</v>
-      </c>
-      <c r="O48" s="3">
-        <v>1300</v>
       </c>
       <c r="P48" s="3">
         <v>1400</v>
       </c>
       <c r="Q48" s="3">
+        <v>1300</v>
+      </c>
+      <c r="R48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="S48" s="3">
         <v>1000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>100</v>
       </c>
-      <c r="Y48" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z48" s="3">
-        <v>0</v>
-      </c>
       <c r="AA48" s="3">
         <v>0</v>
       </c>
@@ -4519,11 +4734,11 @@
       <c r="AF48" s="3">
         <v>0</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH48" s="3" t="s">
-        <v>4</v>
+      <c r="AG48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH48" s="3">
+        <v>0</v>
       </c>
       <c r="AI48" s="3" t="s">
         <v>4</v>
@@ -4531,37 +4746,43 @@
       <c r="AJ48" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL48" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>6100</v>
+        <v>0</v>
       </c>
       <c r="E49" s="3">
-        <v>6100</v>
+        <v>0</v>
       </c>
       <c r="F49" s="3">
         <v>6100</v>
       </c>
       <c r="G49" s="3">
+        <v>6100</v>
+      </c>
+      <c r="H49" s="3">
+        <v>6100</v>
+      </c>
+      <c r="I49" s="3">
         <v>2100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>2100</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>4</v>
+      <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3">
+        <v>0</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>4</v>
@@ -4569,11 +4790,11 @@
       <c r="N49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
-      </c>
-      <c r="P49" s="3">
-        <v>0</v>
+      <c r="O49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q49" s="3">
         <v>0</v>
@@ -4635,8 +4856,14 @@
       <c r="AJ49" s="3">
         <v>0</v>
       </c>
+      <c r="AK49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4966,14 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,52 +5076,58 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>200</v>
+      </c>
+      <c r="E52" s="3">
+        <v>200</v>
+      </c>
+      <c r="F52" s="3">
         <v>1000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>1000</v>
-      </c>
-      <c r="F52" s="3">
-        <v>900</v>
-      </c>
-      <c r="G52" s="3">
-        <v>900</v>
       </c>
       <c r="H52" s="3">
         <v>900</v>
       </c>
       <c r="I52" s="3">
+        <v>900</v>
+      </c>
+      <c r="J52" s="3">
+        <v>900</v>
+      </c>
+      <c r="K52" s="3">
         <v>500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>8600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>8400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>500</v>
-      </c>
-      <c r="P52" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>100</v>
       </c>
       <c r="R52" s="3">
         <v>100</v>
@@ -4912,43 +5151,49 @@
         <v>100</v>
       </c>
       <c r="Y52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Z52" s="3">
         <v>100</v>
       </c>
       <c r="AA52" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AB52" s="3">
         <v>100</v>
       </c>
       <c r="AC52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG52" s="3">
         <v>300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>100</v>
       </c>
-      <c r="AG52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI52" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ52" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL52" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5296,124 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>3700</v>
+      </c>
+      <c r="F54" s="3">
         <v>22800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>19000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>26200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>28800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>34900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>29300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>29300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>31000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>31400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>35600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>40200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>31700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>25000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>30600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>28900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>33900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>25800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>11400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>14900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>14700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>18900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>10000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>15000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>20000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>21500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>24800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>28000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>5600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>7700</v>
       </c>
-      <c r="AG54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI54" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ54" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL54" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5450,10 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,178 +5490,186 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F57" s="3">
         <v>1600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>2100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1800</v>
-      </c>
-      <c r="H57" s="3">
-        <v>1400</v>
-      </c>
-      <c r="I57" s="3">
-        <v>1300</v>
       </c>
       <c r="J57" s="3">
         <v>1400</v>
       </c>
       <c r="K57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="L57" s="3">
         <v>1400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="N57" s="3">
         <v>1100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>2700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>1500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>1600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>1700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>1700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>1800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>1500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>1500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>1100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>1300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>1500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>1600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>1800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>2100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>1500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>300</v>
       </c>
-      <c r="AG57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI57" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ57" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL57" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E58" s="3">
+        <v>10500</v>
+      </c>
+      <c r="F58" s="3">
         <v>10000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>10100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>8700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>5800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>3500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>2400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>7200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>7400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>7700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>7200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>7300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>1000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>400</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y58" s="3" t="s">
         <v>4</v>
       </c>
@@ -5415,11 +5682,11 @@
       <c r="AB58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD58" s="3">
-        <v>0</v>
+      <c r="AC58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE58" s="3">
         <v>0</v>
@@ -5439,249 +5706,267 @@
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E59" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F59" s="3">
         <v>2300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>4500</v>
-      </c>
-      <c r="G59" s="3">
-        <v>100</v>
-      </c>
-      <c r="H59" s="3">
-        <v>200</v>
       </c>
       <c r="I59" s="3">
         <v>100</v>
       </c>
       <c r="J59" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K59" s="3">
+        <v>100</v>
+      </c>
+      <c r="L59" s="3">
+        <v>0</v>
+      </c>
+      <c r="M59" s="3">
         <v>2700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>2700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>2400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>11800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>11900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>13800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>16600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>5100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>1300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>1400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>1600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>300</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI59" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ59" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL59" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>16000</v>
+      </c>
+      <c r="F60" s="3">
         <v>15800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>15800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>16500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>9500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>6500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>4100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>4900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>4500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>11000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>12000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>10400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>11200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>20700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>14600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>16400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>18200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>6700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>2800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>2500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>2900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>2400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>2400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>2500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>3100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>1700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>1300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>1100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>600</v>
       </c>
-      <c r="AG60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI60" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ60" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL60" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>600</v>
+      </c>
+      <c r="E61" s="3">
+        <v>700</v>
+      </c>
+      <c r="F61" s="3">
         <v>3000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>5500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>7900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>10200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>12500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>14800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>8600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>8400</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -5692,26 +5977,26 @@
         <v>0</v>
       </c>
       <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
         <v>7000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>300</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -5751,20 +6036,26 @@
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F62" s="3">
         <v>300</v>
       </c>
-      <c r="E62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G62" s="3" t="s">
         <v>4</v>
       </c>
@@ -5777,18 +6068,18 @@
       <c r="J62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M62" s="3">
         <v>900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>100</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
-      <c r="N62" s="3">
-        <v>0</v>
-      </c>
       <c r="O62" s="3">
         <v>0</v>
       </c>
@@ -5831,32 +6122,38 @@
       <c r="AB62" s="3">
         <v>0</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF62" s="3">
+      <c r="AC62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH62" s="3">
         <v>6400</v>
       </c>
-      <c r="AG62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI62" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ62" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL62" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6256,14 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6366,14 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6476,124 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>16800</v>
+      </c>
+      <c r="F66" s="3">
         <v>19100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>21400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>24400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>19800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>19100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>18800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>13500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>13800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>11100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>12000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>10400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>11200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>20700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>21600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>16700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>18600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>7200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>3100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>2600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>3000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>2500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>2400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>2600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>3100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>1700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>1300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>1100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>7000</v>
       </c>
-      <c r="AG66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI66" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ66" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL66" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6630,10 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6736,14 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6846,14 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6621,8 +6956,14 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,112 +7066,124 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-198800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-195300</v>
+      </c>
+      <c r="F72" s="3">
         <v>-175400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-167500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-156400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-145500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-137500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-130200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-124000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-118200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-112100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-104800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-97600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-90200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-93200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-87600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-82800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-77400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-73200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-68100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-63100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-57700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-52400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-47800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-42400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-36500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-30300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-26000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-22700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-19300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>-17100</v>
       </c>
-      <c r="AG72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI72" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ72" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL72" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7286,14 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7396,14 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7506,124 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="F76" s="3">
         <v>3700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-2400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>1800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>9000</v>
-      </c>
-      <c r="H76" s="3">
-        <v>15800</v>
-      </c>
-      <c r="I76" s="3">
-        <v>10500</v>
       </c>
       <c r="J76" s="3">
         <v>15800</v>
       </c>
       <c r="K76" s="3">
+        <v>10500</v>
+      </c>
+      <c r="L76" s="3">
+        <v>15800</v>
+      </c>
+      <c r="M76" s="3">
         <v>17200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>20300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>23600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>29800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>20500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>4200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>9000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>12100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>15300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>18700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>8300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>12300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>11700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>16400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>7600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>12500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>16900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>19700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>23500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>26900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>5100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>700</v>
       </c>
-      <c r="AG76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI76" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ76" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL76" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7726,239 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="F81" s="3">
         <v>-7900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-11100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-10900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-8000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-7300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-6200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-5700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-6100</v>
-      </c>
-      <c r="L81" s="3">
-        <v>-7300</v>
-      </c>
-      <c r="M81" s="3">
-        <v>-7200</v>
       </c>
       <c r="N81" s="3">
         <v>-7300</v>
       </c>
       <c r="O81" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="P81" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="Q81" s="3">
         <v>3000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-4800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-5400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-4200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-5100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-5000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-5500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-5200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-4600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-5300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-5900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-6200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-4300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-3300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-3400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>-1200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,19 +7995,21 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>200</v>
+      </c>
+      <c r="E83" s="3">
         <v>300</v>
       </c>
-      <c r="E83" s="3">
-        <v>100</v>
-      </c>
       <c r="F83" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="G83" s="3">
         <v>100</v>
@@ -7621,16 +8018,16 @@
         <v>100</v>
       </c>
       <c r="I83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J83" s="3">
+        <v>100</v>
+      </c>
+      <c r="K83" s="3">
+        <v>0</v>
+      </c>
+      <c r="L83" s="3">
         <v>200</v>
-      </c>
-      <c r="K83" s="3">
-        <v>100</v>
-      </c>
-      <c r="L83" s="3">
-        <v>100</v>
       </c>
       <c r="M83" s="3">
         <v>100</v>
@@ -7645,10 +8042,10 @@
         <v>100</v>
       </c>
       <c r="Q83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S83" s="3">
         <v>0</v>
@@ -7704,8 +8101,14 @@
       <c r="AJ83" s="3">
         <v>0</v>
       </c>
+      <c r="AK83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8211,14 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8321,14 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8431,14 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8541,14 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8651,124 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="F89" s="3">
         <v>-5900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-8200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-9900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-6300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-5800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-4700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-7000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-5400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-6800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-4700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-8200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-5900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-5300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-4600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>5500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-1900</v>
-      </c>
-      <c r="U89" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="V89" s="3">
-        <v>-5900</v>
       </c>
       <c r="W89" s="3">
         <v>-4000</v>
       </c>
       <c r="X89" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="Y89" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="Z89" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-5900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-4100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-2400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>-900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>-900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,76 +8805,78 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
       </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-1200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-300</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-200</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-200</v>
       </c>
       <c r="N91" s="3">
         <v>-200</v>
       </c>
       <c r="O91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="P91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-100</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="U91" s="3">
-        <v>0</v>
       </c>
       <c r="V91" s="3">
         <v>-100</v>
       </c>
       <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y91" s="3" t="s">
-        <v>4</v>
+      <c r="Y91" s="3">
+        <v>-100</v>
       </c>
       <c r="Z91" s="3" t="s">
         <v>4</v>
@@ -8452,11 +8893,11 @@
       <c r="AD91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF91" s="3">
-        <v>0</v>
+      <c r="AE91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AG91" s="3">
         <v>0</v>
@@ -8470,8 +8911,14 @@
       <c r="AJ91" s="3">
         <v>0</v>
       </c>
+      <c r="AK91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +9021,14 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,85 +9131,91 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E94" s="3">
         <v>0</v>
       </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>-100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-1700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-1300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>14700</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-200</v>
-      </c>
-      <c r="M94" s="3">
-        <v>-200</v>
       </c>
       <c r="N94" s="3">
         <v>-200</v>
       </c>
       <c r="O94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="P94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-100</v>
-      </c>
-      <c r="T94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="U94" s="3">
-        <v>0</v>
       </c>
       <c r="V94" s="3">
         <v>-100</v>
       </c>
       <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
         <v>-100</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y94" s="3" t="s">
-        <v>4</v>
+      <c r="Y94" s="3">
+        <v>-100</v>
       </c>
       <c r="Z94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB94" s="3">
-        <v>0</v>
+      <c r="AA94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC94" s="3">
         <v>0</v>
@@ -8782,8 +9241,14 @@
       <c r="AJ94" s="3">
         <v>0</v>
       </c>
+      <c r="AK94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,8 +9285,10 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8846,11 +9313,11 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -8924,8 +9391,14 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9501,14 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9611,14 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,112 +9721,124 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E100" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F100" s="3">
         <v>10800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>2500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>3100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>10800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>5000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>3400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>3300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>2900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>15600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>12300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>7900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>1500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>14700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>5500</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>13000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>2800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>100</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3">
         <v>24700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>6800</v>
       </c>
-      <c r="AG100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH100" s="3">
-        <v>0</v>
-      </c>
       <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK100" s="3">
         <v>100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9366,11 +9863,11 @@
       <c r="J101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9444,108 +9941,120 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="F102" s="3">
         <v>4900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-5700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-6900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-5900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>3200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-1000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-4400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-2400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-4100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-5200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>7300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>6000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-5800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>2300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-3500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>5500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>12700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-3500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-4100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>9100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-5400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-3500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>22400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>5900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>-900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>-900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>1800</v>
       </c>
     </row>
